--- a/research/traditional_assets/database/data/malawi/malawi_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/malawi/malawi_hotel_gaming.xlsx
@@ -1127,7 +1127,7 @@
         <v>36.2</v>
       </c>
       <c r="L2">
-        <v>7.96935484667041</v>
+        <v>7.9693548466704</v>
       </c>
       <c r="M2">
         <v>36.2</v>
@@ -1167,13 +1167,13 @@
         <v>0.168112480496496</v>
       </c>
       <c r="X2">
-        <v>0.746038950842442</v>
+        <v>0.746038950842443</v>
       </c>
       <c r="Y2">
         <v>0.7480479046815171</v>
       </c>
       <c r="Z2">
-        <v>4.28257425430168</v>
+        <v>4.28257425430169</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -1251,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1388,22 +1388,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1681124804964965</v>
+        <v>0.167984868016</v>
       </c>
       <c r="C2">
-        <v>36.2</v>
+        <v>35.87580805159414</v>
       </c>
       <c r="D2">
-        <v>36.2</v>
+        <v>36.23780805159414</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.362</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.362</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1424,28 +1424,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0182086</v>
       </c>
       <c r="N2">
-        <v>7.603000000000001</v>
+        <v>7.5847914</v>
       </c>
       <c r="O2">
-        <v>0.7603000000000001</v>
+        <v>0.7584791400000001</v>
       </c>
       <c r="P2">
-        <v>6.842700000000001</v>
+        <v>6.82631226</v>
       </c>
       <c r="Q2">
-        <v>7.379700000000001</v>
+        <v>7.36331226</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1681124804964965</v>
+        <v>0.1692244121373737</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815168</v>
+        <v>0.7548483401786215</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>417.5499489252331</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1470,22 +1470,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.167984868016</v>
+        <v>0.1678572555355035</v>
       </c>
       <c r="C3">
-        <v>35.87580805159414</v>
+        <v>35.55169516082769</v>
       </c>
       <c r="D3">
-        <v>36.23780805159414</v>
+        <v>36.27569516082769</v>
       </c>
       <c r="E3">
-        <v>0.362</v>
+        <v>0.7240000000000001</v>
       </c>
       <c r="F3">
-        <v>0.362</v>
+        <v>0.7240000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1506,28 +1506,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M3">
-        <v>0.0182086</v>
+        <v>0.0364172</v>
       </c>
       <c r="N3">
-        <v>7.5847914</v>
+        <v>7.566582800000001</v>
       </c>
       <c r="O3">
-        <v>0.7584791400000001</v>
+        <v>0.7566582800000001</v>
       </c>
       <c r="P3">
-        <v>6.82631226</v>
+        <v>6.809924520000001</v>
       </c>
       <c r="Q3">
-        <v>7.36331226</v>
+        <v>7.346924520000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1692244121373737</v>
+        <v>0.1703590362607179</v>
       </c>
       <c r="T3">
-        <v>0.7548483401786215</v>
+        <v>0.7617875600736264</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>417.5499489252331</v>
+        <v>208.7749744626166</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1552,22 +1552,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1678572555355035</v>
+        <v>0.167729643055007</v>
       </c>
       <c r="C4">
-        <v>35.55169516082769</v>
+        <v>35.22766157592758</v>
       </c>
       <c r="D4">
-        <v>36.27569516082769</v>
+        <v>36.31366157592758</v>
       </c>
       <c r="E4">
-        <v>0.7240000000000001</v>
+        <v>1.086</v>
       </c>
       <c r="F4">
-        <v>0.7240000000000001</v>
+        <v>1.086</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1588,28 +1588,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M4">
-        <v>0.0364172</v>
+        <v>0.0546258</v>
       </c>
       <c r="N4">
-        <v>7.566582800000001</v>
+        <v>7.5483742</v>
       </c>
       <c r="O4">
-        <v>0.7566582800000001</v>
+        <v>0.7548374200000001</v>
       </c>
       <c r="P4">
-        <v>6.809924520000001</v>
+        <v>6.79353678</v>
       </c>
       <c r="Q4">
-        <v>7.346924520000001</v>
+        <v>7.33053678</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1703590362607179</v>
+        <v>0.1715170546958835</v>
       </c>
       <c r="T4">
-        <v>0.7617875600736264</v>
+        <v>0.7688698566674971</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>208.7749744626166</v>
+        <v>139.183316308411</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1634,22 +1634,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.167729643055007</v>
+        <v>0.1676020305745105</v>
       </c>
       <c r="C5">
-        <v>35.22766157592758</v>
+        <v>34.90370754616105</v>
       </c>
       <c r="D5">
-        <v>36.31366157592758</v>
+        <v>36.35170754616105</v>
       </c>
       <c r="E5">
-        <v>1.086</v>
+        <v>1.448</v>
       </c>
       <c r="F5">
-        <v>1.086</v>
+        <v>1.448</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1670,28 +1670,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M5">
-        <v>0.0546258</v>
+        <v>0.07283440000000001</v>
       </c>
       <c r="N5">
-        <v>7.5483742</v>
+        <v>7.530165600000001</v>
       </c>
       <c r="O5">
-        <v>0.7548374200000001</v>
+        <v>0.7530165600000002</v>
       </c>
       <c r="P5">
-        <v>6.79353678</v>
+        <v>6.777149040000001</v>
       </c>
       <c r="Q5">
-        <v>7.33053678</v>
+        <v>7.314149040000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1715170546958835</v>
+        <v>0.1726991985151151</v>
       </c>
       <c r="T5">
-        <v>0.7688698566674971</v>
+        <v>0.7760997011070738</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>139.183316308411</v>
+        <v>104.3874872313083</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1716,22 +1716,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1676020305745105</v>
+        <v>0.167474418094014</v>
       </c>
       <c r="C6">
-        <v>34.90370754616105</v>
+        <v>34.57983332184106</v>
       </c>
       <c r="D6">
-        <v>36.35170754616105</v>
+        <v>36.38983332184107</v>
       </c>
       <c r="E6">
-        <v>1.448</v>
+        <v>1.81</v>
       </c>
       <c r="F6">
-        <v>1.448</v>
+        <v>1.81</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1752,28 +1752,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M6">
-        <v>0.07283440000000001</v>
+        <v>0.09104300000000001</v>
       </c>
       <c r="N6">
-        <v>7.530165600000001</v>
+        <v>7.511957000000001</v>
       </c>
       <c r="O6">
-        <v>0.7530165600000002</v>
+        <v>0.7511957000000001</v>
       </c>
       <c r="P6">
-        <v>6.777149040000001</v>
+        <v>6.7607613</v>
       </c>
       <c r="Q6">
-        <v>7.314149040000001</v>
+        <v>7.2977613</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1726991985151151</v>
+        <v>0.1739062295726463</v>
       </c>
       <c r="T6">
-        <v>0.7760997011070738</v>
+        <v>0.7834817527980097</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>104.3874872313083</v>
+        <v>83.50998978504663</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1798,22 +1798,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.167474418094014</v>
+        <v>0.1673468056135175</v>
       </c>
       <c r="C7">
-        <v>34.57983332184106</v>
+        <v>34.25603915433181</v>
       </c>
       <c r="D7">
-        <v>36.38983332184107</v>
+        <v>36.42803915433181</v>
       </c>
       <c r="E7">
-        <v>1.81</v>
+        <v>2.172</v>
       </c>
       <c r="F7">
-        <v>1.81</v>
+        <v>2.172</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1834,28 +1834,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M7">
-        <v>0.09104300000000001</v>
+        <v>0.1092516</v>
       </c>
       <c r="N7">
-        <v>7.511957000000001</v>
+        <v>7.4937484</v>
       </c>
       <c r="O7">
-        <v>0.7511957000000001</v>
+        <v>0.7493748400000001</v>
       </c>
       <c r="P7">
-        <v>6.7607613</v>
+        <v>6.744373560000001</v>
       </c>
       <c r="Q7">
-        <v>7.2977613</v>
+        <v>7.28137356</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1739062295726463</v>
+        <v>0.1751389421420399</v>
       </c>
       <c r="T7">
-        <v>0.7834817527980097</v>
+        <v>0.7910208694185401</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>83.50998978504663</v>
+        <v>69.59165815420552</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1880,22 +1880,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1673468056135175</v>
+        <v>0.167219193133021</v>
       </c>
       <c r="C8">
-        <v>34.25603915433181</v>
+        <v>33.93232529605419</v>
       </c>
       <c r="D8">
-        <v>36.42803915433181</v>
+        <v>36.46632529605419</v>
       </c>
       <c r="E8">
-        <v>2.172</v>
+        <v>2.534</v>
       </c>
       <c r="F8">
-        <v>2.172</v>
+        <v>2.534</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1916,28 +1916,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M8">
-        <v>0.1092516</v>
+        <v>0.1274602</v>
       </c>
       <c r="N8">
-        <v>7.4937484</v>
+        <v>7.475539800000001</v>
       </c>
       <c r="O8">
-        <v>0.7493748400000001</v>
+        <v>0.7475539800000002</v>
       </c>
       <c r="P8">
-        <v>6.744373560000001</v>
+        <v>6.727985820000001</v>
       </c>
       <c r="Q8">
-        <v>7.28137356</v>
+        <v>7.264985820000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1751389421420399</v>
+        <v>0.1763981646591624</v>
       </c>
       <c r="T8">
-        <v>0.7910208694185401</v>
+        <v>0.7987221175792969</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>69.59165815420552</v>
+        <v>59.64999270360474</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1962,22 +1962,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.167219193133021</v>
+        <v>0.1670915806525245</v>
       </c>
       <c r="C9">
-        <v>33.93232529605419</v>
+        <v>33.60869200049143</v>
       </c>
       <c r="D9">
-        <v>36.46632529605419</v>
+        <v>36.50469200049143</v>
       </c>
       <c r="E9">
-        <v>2.534</v>
+        <v>2.896</v>
       </c>
       <c r="F9">
-        <v>2.534</v>
+        <v>2.896</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1998,28 +1998,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M9">
-        <v>0.1274602</v>
+        <v>0.1456688</v>
       </c>
       <c r="N9">
-        <v>7.475539800000001</v>
+        <v>7.4573312</v>
       </c>
       <c r="O9">
-        <v>0.7475539800000002</v>
+        <v>0.7457331200000001</v>
       </c>
       <c r="P9">
-        <v>6.727985820000001</v>
+        <v>6.71159808</v>
       </c>
       <c r="Q9">
-        <v>7.264985820000001</v>
+        <v>7.24859808</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1763981646591624</v>
+        <v>0.177684761578831</v>
       </c>
       <c r="T9">
-        <v>0.7987221175792971</v>
+        <v>0.8065907841783312</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>59.64999270360474</v>
+        <v>52.19374361565414</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2044,22 +2044,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1670915806525245</v>
+        <v>0.166963968172028</v>
       </c>
       <c r="C10">
-        <v>33.60869200049143</v>
+        <v>33.28513952219466</v>
       </c>
       <c r="D10">
-        <v>36.50469200049143</v>
+        <v>36.54313952219466</v>
       </c>
       <c r="E10">
-        <v>2.896</v>
+        <v>3.258</v>
       </c>
       <c r="F10">
-        <v>2.896</v>
+        <v>3.258</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2080,28 +2080,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M10">
-        <v>0.1456688</v>
+        <v>0.1638774</v>
       </c>
       <c r="N10">
-        <v>7.4573312</v>
+        <v>7.439122600000001</v>
       </c>
       <c r="O10">
-        <v>0.7457331200000001</v>
+        <v>0.7439122600000001</v>
       </c>
       <c r="P10">
-        <v>6.71159808</v>
+        <v>6.695210340000001</v>
       </c>
       <c r="Q10">
-        <v>7.24859808</v>
+        <v>7.232210340000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.177684761578831</v>
+        <v>0.1789996353538769</v>
       </c>
       <c r="T10">
-        <v>0.8065907841783312</v>
+        <v>0.8146323885048166</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>52.19374361565414</v>
+        <v>46.39443876947036</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2126,22 +2126,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.166963968172028</v>
+        <v>0.1668363556915315</v>
       </c>
       <c r="C11">
-        <v>33.28513952219466</v>
+        <v>32.96166811678852</v>
       </c>
       <c r="D11">
-        <v>36.54313952219466</v>
+        <v>36.58166811678851</v>
       </c>
       <c r="E11">
-        <v>3.258</v>
+        <v>3.62</v>
       </c>
       <c r="F11">
-        <v>3.258</v>
+        <v>3.62</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2162,28 +2162,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M11">
-        <v>0.1638774</v>
+        <v>0.182086</v>
       </c>
       <c r="N11">
-        <v>7.439122600000001</v>
+        <v>7.420914000000001</v>
       </c>
       <c r="O11">
-        <v>0.7439122600000001</v>
+        <v>0.7420914000000001</v>
       </c>
       <c r="P11">
-        <v>6.695210340000001</v>
+        <v>6.6788226</v>
       </c>
       <c r="Q11">
-        <v>7.232210340000001</v>
+        <v>7.2158226</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1789996353538769</v>
+        <v>0.1803437285461462</v>
       </c>
       <c r="T11">
-        <v>0.8146323885048166</v>
+        <v>0.8228526951496685</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>46.39443876947036</v>
+        <v>41.75499489252331</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2208,22 +2208,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1668363556915315</v>
+        <v>0.166708743211035</v>
       </c>
       <c r="C12">
-        <v>32.96166811678852</v>
+        <v>32.63827804097684</v>
       </c>
       <c r="D12">
-        <v>36.58166811678851</v>
+        <v>36.62027804097684</v>
       </c>
       <c r="E12">
-        <v>3.620000000000001</v>
+        <v>3.982</v>
       </c>
       <c r="F12">
-        <v>3.620000000000001</v>
+        <v>3.982</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2244,28 +2244,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M12">
-        <v>0.182086</v>
+        <v>0.2002946</v>
       </c>
       <c r="N12">
-        <v>7.420914000000001</v>
+        <v>7.4027054</v>
       </c>
       <c r="O12">
-        <v>0.7420914000000001</v>
+        <v>0.74027054</v>
       </c>
       <c r="P12">
-        <v>6.6788226</v>
+        <v>6.66243486</v>
       </c>
       <c r="Q12">
-        <v>7.2158226</v>
+        <v>7.19943486</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1803437285461462</v>
+        <v>0.1817180260798147</v>
       </c>
       <c r="T12">
-        <v>0.8228526951496685</v>
+        <v>0.8312577277865394</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>41.75499489252331</v>
+        <v>37.95908626593029</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2290,22 +2290,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.166708743211035</v>
+        <v>0.1665811307305386</v>
       </c>
       <c r="C13">
-        <v>32.63827804097684</v>
+        <v>32.31496955254833</v>
       </c>
       <c r="D13">
-        <v>36.62027804097684</v>
+        <v>36.65896955254834</v>
       </c>
       <c r="E13">
-        <v>3.982</v>
+        <v>4.344</v>
       </c>
       <c r="F13">
-        <v>3.982</v>
+        <v>4.344</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2326,28 +2326,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M13">
-        <v>0.2002946</v>
+        <v>0.2185032</v>
       </c>
       <c r="N13">
-        <v>7.4027054</v>
+        <v>7.384496800000001</v>
       </c>
       <c r="O13">
-        <v>0.74027054</v>
+        <v>0.7384496800000001</v>
       </c>
       <c r="P13">
-        <v>6.66243486</v>
+        <v>6.64604712</v>
       </c>
       <c r="Q13">
-        <v>7.19943486</v>
+        <v>7.18304712</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1817180260798147</v>
+        <v>0.1831235576483393</v>
       </c>
       <c r="T13">
-        <v>0.8312577277865394</v>
+        <v>0.8398537838924303</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>37.95908626593029</v>
+        <v>34.79582907710277</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2372,22 +2372,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1665811307305386</v>
+        <v>0.166453518250042</v>
       </c>
       <c r="C14">
-        <v>32.31496955254833</v>
+        <v>31.9917429103824</v>
       </c>
       <c r="D14">
-        <v>36.65896955254834</v>
+        <v>36.6977429103824</v>
       </c>
       <c r="E14">
-        <v>4.344</v>
+        <v>4.706</v>
       </c>
       <c r="F14">
-        <v>4.344</v>
+        <v>4.706</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2408,28 +2408,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M14">
-        <v>0.2185032</v>
+        <v>0.2367118</v>
       </c>
       <c r="N14">
-        <v>7.384496800000001</v>
+        <v>7.366288200000001</v>
       </c>
       <c r="O14">
-        <v>0.7384496800000001</v>
+        <v>0.7366288200000001</v>
       </c>
       <c r="P14">
-        <v>6.64604712</v>
+        <v>6.629659380000001</v>
       </c>
       <c r="Q14">
-        <v>7.18304712</v>
+        <v>7.16665938</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1831235576483393</v>
+        <v>0.1845614002874046</v>
       </c>
       <c r="T14">
-        <v>0.8398537838924303</v>
+        <v>0.8486474504835139</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>34.79582907710277</v>
+        <v>32.11922684040255</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2454,22 +2454,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.166453518250042</v>
+        <v>0.1663259057695456</v>
       </c>
       <c r="C15">
-        <v>31.9917429103824</v>
+        <v>31.66859837445474</v>
       </c>
       <c r="D15">
-        <v>36.6977429103824</v>
+        <v>36.73659837445474</v>
       </c>
       <c r="E15">
-        <v>4.706</v>
+        <v>5.068000000000001</v>
       </c>
       <c r="F15">
-        <v>4.706</v>
+        <v>5.068000000000001</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2490,28 +2490,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M15">
-        <v>0.2367118</v>
+        <v>0.2549204</v>
       </c>
       <c r="N15">
-        <v>7.366288200000001</v>
+        <v>7.348079600000001</v>
       </c>
       <c r="O15">
-        <v>0.7366288200000001</v>
+        <v>0.7348079600000001</v>
       </c>
       <c r="P15">
-        <v>6.629659380000001</v>
+        <v>6.613271640000001</v>
       </c>
       <c r="Q15">
-        <v>7.16665938</v>
+        <v>7.150271640000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1845614002874046</v>
+        <v>0.1860326811273786</v>
       </c>
       <c r="T15">
-        <v>0.8486474504835139</v>
+        <v>0.8576456209488088</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>32.11922684040255</v>
+        <v>29.82499635180237</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2536,22 +2536,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1663259057695456</v>
+        <v>0.1661982932890491</v>
       </c>
       <c r="C16">
-        <v>31.66859837445474</v>
+        <v>31.34553620584337</v>
       </c>
       <c r="D16">
-        <v>36.73659837445474</v>
+        <v>36.77553620584337</v>
       </c>
       <c r="E16">
-        <v>5.068000000000001</v>
+        <v>5.430000000000001</v>
       </c>
       <c r="F16">
-        <v>5.068000000000001</v>
+        <v>5.430000000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2572,28 +2572,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M16">
-        <v>0.2549204</v>
+        <v>0.2731290000000001</v>
       </c>
       <c r="N16">
-        <v>7.348079600000001</v>
+        <v>7.329871000000001</v>
       </c>
       <c r="O16">
-        <v>0.7348079600000001</v>
+        <v>0.7329871000000001</v>
       </c>
       <c r="P16">
-        <v>6.613271640000001</v>
+        <v>6.596883900000001</v>
       </c>
       <c r="Q16">
-        <v>7.150271640000001</v>
+        <v>7.133883900000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1860326811273786</v>
+        <v>0.1875385803400577</v>
       </c>
       <c r="T16">
-        <v>0.8576456209488088</v>
+        <v>0.8668555130721107</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>29.82499635180237</v>
+        <v>27.8366632616822</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2618,22 +2618,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1661982932890491</v>
+        <v>0.1660706808085526</v>
       </c>
       <c r="C17">
-        <v>31.34553620584337</v>
+        <v>31.02255666673431</v>
       </c>
       <c r="D17">
-        <v>36.77553620584337</v>
+        <v>36.81455666673431</v>
       </c>
       <c r="E17">
-        <v>5.430000000000001</v>
+        <v>5.792000000000001</v>
       </c>
       <c r="F17">
-        <v>5.430000000000001</v>
+        <v>5.792000000000001</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M17">
-        <v>0.273129</v>
+        <v>0.2913376</v>
       </c>
       <c r="N17">
-        <v>7.329871000000001</v>
+        <v>7.3116624</v>
       </c>
       <c r="O17">
-        <v>0.7329871000000001</v>
+        <v>0.7311662400000001</v>
       </c>
       <c r="P17">
-        <v>6.596883900000001</v>
+        <v>6.58049616</v>
       </c>
       <c r="Q17">
-        <v>7.133883900000001</v>
+        <v>7.11749616</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1875385803400577</v>
+        <v>0.1890803342958959</v>
       </c>
       <c r="T17">
-        <v>0.8668555130721107</v>
+        <v>0.8762846883412054</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>27.83666326168221</v>
+        <v>26.09687180782707</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2700,22 +2700,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1660706808085526</v>
+        <v>0.1659430683280561</v>
       </c>
       <c r="C18">
-        <v>31.02255666673431</v>
+        <v>30.69966002042753</v>
       </c>
       <c r="D18">
-        <v>36.81455666673431</v>
+        <v>36.85366002042753</v>
       </c>
       <c r="E18">
-        <v>5.792000000000001</v>
+        <v>6.154000000000001</v>
       </c>
       <c r="F18">
-        <v>5.792000000000001</v>
+        <v>6.154000000000001</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2736,28 +2736,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M18">
-        <v>0.2913376</v>
+        <v>0.3095462</v>
       </c>
       <c r="N18">
-        <v>7.3116624</v>
+        <v>7.293453800000001</v>
       </c>
       <c r="O18">
-        <v>0.7311662400000001</v>
+        <v>0.7293453800000002</v>
       </c>
       <c r="P18">
-        <v>6.58049616</v>
+        <v>6.564108420000001</v>
       </c>
       <c r="Q18">
-        <v>7.11749616</v>
+        <v>7.101108420000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1890803342958959</v>
+        <v>0.1906592389494652</v>
       </c>
       <c r="T18">
-        <v>0.8762846883412054</v>
+        <v>0.885941072652929</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>26.09687180782707</v>
+        <v>24.5617617014843</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2782,22 +2782,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1659430683280561</v>
+        <v>0.1658154558475596</v>
       </c>
       <c r="C19">
-        <v>30.69966002042753</v>
+        <v>30.37684653134289</v>
       </c>
       <c r="D19">
-        <v>36.85366002042753</v>
+        <v>36.89284653134289</v>
       </c>
       <c r="E19">
-        <v>6.154000000000001</v>
+        <v>6.516000000000001</v>
       </c>
       <c r="F19">
-        <v>6.154000000000001</v>
+        <v>6.516000000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2818,28 +2818,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M19">
-        <v>0.3095462</v>
+        <v>0.3277548</v>
       </c>
       <c r="N19">
-        <v>7.293453800000001</v>
+        <v>7.275245200000001</v>
       </c>
       <c r="O19">
-        <v>0.7293453800000002</v>
+        <v>0.7275245200000001</v>
       </c>
       <c r="P19">
-        <v>6.564108420000001</v>
+        <v>6.54772068</v>
       </c>
       <c r="Q19">
-        <v>7.101108420000001</v>
+        <v>7.08472068</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1906592389494652</v>
+        <v>0.1922766534726336</v>
       </c>
       <c r="T19">
-        <v>0.885941072652929</v>
+        <v>0.8958329785332311</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>24.5617617014843</v>
+        <v>23.19721938473517</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2864,22 +2864,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1658154558475596</v>
+        <v>0.1656878433670631</v>
       </c>
       <c r="C20">
-        <v>30.37684653134288</v>
+        <v>30.05411646502604</v>
       </c>
       <c r="D20">
-        <v>36.89284653134288</v>
+        <v>36.93211646502604</v>
       </c>
       <c r="E20">
-        <v>6.516</v>
+        <v>6.878000000000001</v>
       </c>
       <c r="F20">
-        <v>6.516</v>
+        <v>6.878000000000001</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2900,28 +2900,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M20">
-        <v>0.3277548</v>
+        <v>0.3459634</v>
       </c>
       <c r="N20">
-        <v>7.275245200000001</v>
+        <v>7.257036600000001</v>
       </c>
       <c r="O20">
-        <v>0.7275245200000001</v>
+        <v>0.7257036600000002</v>
       </c>
       <c r="P20">
-        <v>6.54772068</v>
+        <v>6.53133294</v>
       </c>
       <c r="Q20">
-        <v>7.08472068</v>
+        <v>7.06833294</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1922766534726336</v>
+        <v>0.193934004156868</v>
       </c>
       <c r="T20">
-        <v>0.8958329785332311</v>
+        <v>0.9059691290031703</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>23.19721938473518</v>
+        <v>21.97631310132806</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2946,22 +2946,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1656878433670631</v>
+        <v>0.1655602308865666</v>
       </c>
       <c r="C21">
-        <v>30.05411646502604</v>
+        <v>29.7314700881545</v>
       </c>
       <c r="D21">
-        <v>36.93211646502604</v>
+        <v>36.9714700881545</v>
       </c>
       <c r="E21">
-        <v>6.878000000000001</v>
+        <v>7.240000000000001</v>
       </c>
       <c r="F21">
-        <v>6.878000000000001</v>
+        <v>7.240000000000001</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2982,28 +2982,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M21">
-        <v>0.3459634</v>
+        <v>0.3641720000000001</v>
       </c>
       <c r="N21">
-        <v>7.257036600000001</v>
+        <v>7.238828000000001</v>
       </c>
       <c r="O21">
-        <v>0.7257036600000002</v>
+        <v>0.7238828000000002</v>
       </c>
       <c r="P21">
-        <v>6.53133294</v>
+        <v>6.514945200000001</v>
       </c>
       <c r="Q21">
-        <v>7.06833294</v>
+        <v>7.0519452</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.193934004156868</v>
+        <v>0.1956327886082082</v>
       </c>
       <c r="T21">
-        <v>0.9059691290031703</v>
+        <v>0.9163586832348581</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>21.97631310132806</v>
+        <v>20.87749744626166</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3028,22 +3028,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1655602308865666</v>
+        <v>0.1654326184060701</v>
       </c>
       <c r="C22">
-        <v>29.7314700881545</v>
+        <v>29.40890766854363</v>
       </c>
       <c r="D22">
-        <v>36.9714700881545</v>
+        <v>37.01090766854363</v>
       </c>
       <c r="E22">
-        <v>7.240000000000001</v>
+        <v>7.602000000000001</v>
       </c>
       <c r="F22">
-        <v>7.240000000000001</v>
+        <v>7.602000000000001</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3064,28 +3064,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M22">
-        <v>0.3641720000000001</v>
+        <v>0.3823806</v>
       </c>
       <c r="N22">
-        <v>7.238828000000001</v>
+        <v>7.2206194</v>
       </c>
       <c r="O22">
-        <v>0.7238828000000002</v>
+        <v>0.7220619400000001</v>
       </c>
       <c r="P22">
-        <v>6.514945200000001</v>
+        <v>6.498557460000001</v>
       </c>
       <c r="Q22">
-        <v>7.0519452</v>
+        <v>7.035557460000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1956327886082082</v>
+        <v>0.1973745802608482</v>
       </c>
       <c r="T22">
-        <v>0.9163586832348581</v>
+        <v>0.9270112641559556</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>20.87749744626166</v>
+        <v>19.88333090120158</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3110,22 +3110,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1654326184060701</v>
+        <v>0.1653050059255736</v>
       </c>
       <c r="C23">
-        <v>29.40890766854363</v>
+        <v>29.08642947515272</v>
       </c>
       <c r="D23">
-        <v>37.01090766854363</v>
+        <v>37.05042947515272</v>
       </c>
       <c r="E23">
-        <v>7.602</v>
+        <v>7.964</v>
       </c>
       <c r="F23">
-        <v>7.602</v>
+        <v>7.964</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3146,28 +3146,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M23">
-        <v>0.3823806</v>
+        <v>0.4005892</v>
       </c>
       <c r="N23">
-        <v>7.2206194</v>
+        <v>7.202410800000001</v>
       </c>
       <c r="O23">
-        <v>0.7220619400000001</v>
+        <v>0.7202410800000001</v>
       </c>
       <c r="P23">
-        <v>6.498557460000001</v>
+        <v>6.482169720000001</v>
       </c>
       <c r="Q23">
-        <v>7.035557460000001</v>
+        <v>7.019169720000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1973745802608482</v>
+        <v>0.1991610332379149</v>
       </c>
       <c r="T23">
-        <v>0.9270112641559556</v>
+        <v>0.9379369881775942</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>19.88333090120158</v>
+        <v>18.97954313296514</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3192,22 +3192,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1653050059255736</v>
+        <v>0.1651773934450771</v>
       </c>
       <c r="C24">
-        <v>29.08642947515272</v>
+        <v>28.76403577809116</v>
       </c>
       <c r="D24">
-        <v>37.05042947515272</v>
+        <v>37.09003577809116</v>
       </c>
       <c r="E24">
-        <v>7.964</v>
+        <v>8.326000000000001</v>
       </c>
       <c r="F24">
-        <v>7.964</v>
+        <v>8.326000000000001</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3228,28 +3228,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M24">
-        <v>0.4005892</v>
+        <v>0.4187978</v>
       </c>
       <c r="N24">
-        <v>7.202410800000001</v>
+        <v>7.184202200000001</v>
       </c>
       <c r="O24">
-        <v>0.7202410800000001</v>
+        <v>0.7184202200000001</v>
       </c>
       <c r="P24">
-        <v>6.482169720000001</v>
+        <v>6.465781980000001</v>
       </c>
       <c r="Q24">
-        <v>7.019169720000001</v>
+        <v>7.002781980000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1991610332379149</v>
+        <v>0.2009938875910092</v>
       </c>
       <c r="T24">
-        <v>0.9379369881775942</v>
+        <v>0.9491464972387558</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.97954313296514</v>
+        <v>18.15434560544492</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3274,22 +3274,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1651773934450771</v>
+        <v>0.1650497809645806</v>
       </c>
       <c r="C25">
-        <v>28.76403577809116</v>
+        <v>28.44172684862445</v>
       </c>
       <c r="D25">
-        <v>37.09003577809116</v>
+        <v>37.12972684862445</v>
       </c>
       <c r="E25">
-        <v>8.326000000000001</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="F25">
-        <v>8.326000000000001</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3310,28 +3310,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M25">
-        <v>0.4187978</v>
+        <v>0.4370064</v>
       </c>
       <c r="N25">
-        <v>7.184202200000001</v>
+        <v>7.1659936</v>
       </c>
       <c r="O25">
-        <v>0.7184202200000001</v>
+        <v>0.71659936</v>
       </c>
       <c r="P25">
-        <v>6.465781980000001</v>
+        <v>6.44939424</v>
       </c>
       <c r="Q25">
-        <v>7.002781980000001</v>
+        <v>6.98639424</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2009938875910092</v>
+        <v>0.2028749749533955</v>
       </c>
       <c r="T25">
-        <v>0.9491464972387558</v>
+        <v>0.9606509933804742</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>18.15434560544492</v>
+        <v>17.39791453855138</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3356,22 +3356,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1650497809645806</v>
+        <v>0.1649221684840841</v>
       </c>
       <c r="C26">
-        <v>28.44172684862445</v>
+        <v>28.11950295918059</v>
       </c>
       <c r="D26">
-        <v>37.12972684862445</v>
+        <v>37.16950295918059</v>
       </c>
       <c r="E26">
-        <v>8.688000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="F26">
-        <v>8.688000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3392,28 +3392,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M26">
-        <v>0.4370064</v>
+        <v>0.455215</v>
       </c>
       <c r="N26">
-        <v>7.1659936</v>
+        <v>7.147785000000001</v>
       </c>
       <c r="O26">
-        <v>0.71659936</v>
+        <v>0.7147785000000001</v>
       </c>
       <c r="P26">
-        <v>6.44939424</v>
+        <v>6.4330065</v>
       </c>
       <c r="Q26">
-        <v>6.98639424</v>
+        <v>6.9700065</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2028749749533955</v>
+        <v>0.2048062246454455</v>
       </c>
       <c r="T26">
-        <v>0.9606509933804742</v>
+        <v>0.9724622760859719</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>17.39791453855138</v>
+        <v>16.70199795700933</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3438,22 +3438,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1649221684840841</v>
+        <v>0.1647945560035876</v>
       </c>
       <c r="C27">
-        <v>28.11950295918059</v>
+        <v>27.79736438335616</v>
       </c>
       <c r="D27">
-        <v>37.16950295918059</v>
+        <v>37.20936438335616</v>
       </c>
       <c r="E27">
-        <v>9.050000000000001</v>
+        <v>9.412000000000001</v>
       </c>
       <c r="F27">
-        <v>9.050000000000001</v>
+        <v>9.412000000000001</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3474,28 +3474,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M27">
-        <v>0.455215</v>
+        <v>0.4734236</v>
       </c>
       <c r="N27">
-        <v>7.147785000000001</v>
+        <v>7.1295764</v>
       </c>
       <c r="O27">
-        <v>0.7147785000000001</v>
+        <v>0.7129576400000001</v>
       </c>
       <c r="P27">
-        <v>6.4330065</v>
+        <v>6.41661876</v>
       </c>
       <c r="Q27">
-        <v>6.9700065</v>
+        <v>6.95361876</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2048062246454455</v>
+        <v>0.2067896702751184</v>
       </c>
       <c r="T27">
-        <v>0.9724622760859719</v>
+        <v>0.9845927826483749</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.70199795700933</v>
+        <v>16.05961342020127</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3520,22 +3520,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1647945560035876</v>
+        <v>0.1646669435230911</v>
       </c>
       <c r="C28">
-        <v>27.79736438335616</v>
+        <v>27.47531139592267</v>
       </c>
       <c r="D28">
-        <v>37.20936438335616</v>
+        <v>37.24931139592267</v>
       </c>
       <c r="E28">
-        <v>9.412000000000001</v>
+        <v>9.774000000000001</v>
       </c>
       <c r="F28">
-        <v>9.412000000000001</v>
+        <v>9.774000000000001</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3556,28 +3556,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M28">
-        <v>0.4734236</v>
+        <v>0.4916322</v>
       </c>
       <c r="N28">
-        <v>7.1295764</v>
+        <v>7.111367800000001</v>
       </c>
       <c r="O28">
-        <v>0.7129576400000001</v>
+        <v>0.7111367800000001</v>
       </c>
       <c r="P28">
-        <v>6.41661876</v>
+        <v>6.400231020000001</v>
       </c>
       <c r="Q28">
-        <v>6.95361876</v>
+        <v>6.93723102</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2067896702751184</v>
+        <v>0.2088274568809467</v>
       </c>
       <c r="T28">
-        <v>0.9845927826483749</v>
+        <v>0.9970556318563232</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>16.05961342020127</v>
+        <v>15.46481292315678</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3602,22 +3602,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1646669435230911</v>
+        <v>0.1645393310425946</v>
       </c>
       <c r="C29">
-        <v>27.47531139592267</v>
+        <v>27.15334427283279</v>
       </c>
       <c r="D29">
-        <v>37.24931139592267</v>
+        <v>37.28934427283279</v>
       </c>
       <c r="E29">
-        <v>9.774000000000001</v>
+        <v>10.136</v>
       </c>
       <c r="F29">
-        <v>9.774000000000001</v>
+        <v>10.136</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3638,28 +3638,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M29">
-        <v>0.4916322</v>
+        <v>0.5098408</v>
       </c>
       <c r="N29">
-        <v>7.111367800000001</v>
+        <v>7.093159200000001</v>
       </c>
       <c r="O29">
-        <v>0.7111367800000001</v>
+        <v>0.7093159200000001</v>
       </c>
       <c r="P29">
-        <v>6.400231020000001</v>
+        <v>6.383843280000001</v>
       </c>
       <c r="Q29">
-        <v>6.93723102</v>
+        <v>6.920843280000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2088274568809467</v>
+        <v>0.2109218486702703</v>
       </c>
       <c r="T29">
-        <v>0.9970556318563232</v>
+        <v>1.009864671320048</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>15.46481292315678</v>
+        <v>14.91249817590118</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3684,22 +3684,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1645393310425946</v>
+        <v>0.1644117185620981</v>
       </c>
       <c r="C30">
-        <v>27.15334427283279</v>
+        <v>26.83146329122685</v>
       </c>
       <c r="D30">
-        <v>37.28934427283279</v>
+        <v>37.32946329122686</v>
       </c>
       <c r="E30">
-        <v>10.136</v>
+        <v>10.498</v>
       </c>
       <c r="F30">
-        <v>10.136</v>
+        <v>10.498</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3720,28 +3720,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M30">
-        <v>0.5098408</v>
+        <v>0.5280494000000001</v>
       </c>
       <c r="N30">
-        <v>7.093159200000001</v>
+        <v>7.0749506</v>
       </c>
       <c r="O30">
-        <v>0.7093159200000001</v>
+        <v>0.7074950600000001</v>
       </c>
       <c r="P30">
-        <v>6.383843280000001</v>
+        <v>6.36745554</v>
       </c>
       <c r="Q30">
-        <v>6.920843280000001</v>
+        <v>6.90445554</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2109218486702703</v>
+        <v>0.2130752374114058</v>
       </c>
       <c r="T30">
-        <v>1.009864671320048</v>
+        <v>1.023034528796835</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.91249817590118</v>
+        <v>14.39827410087011</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3766,22 +3766,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1644117185620981</v>
+        <v>0.1642841060816016</v>
       </c>
       <c r="C31">
-        <v>26.83146329122686</v>
+        <v>26.50966872943911</v>
       </c>
       <c r="D31">
-        <v>37.32946329122686</v>
+        <v>37.36966872943911</v>
       </c>
       <c r="E31">
-        <v>10.498</v>
+        <v>10.86</v>
       </c>
       <c r="F31">
-        <v>10.498</v>
+        <v>10.86</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3802,28 +3802,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M31">
-        <v>0.5280493999999999</v>
+        <v>0.546258</v>
       </c>
       <c r="N31">
-        <v>7.074950600000001</v>
+        <v>7.056742000000001</v>
       </c>
       <c r="O31">
-        <v>0.7074950600000002</v>
+        <v>0.7056742000000001</v>
       </c>
       <c r="P31">
-        <v>6.367455540000001</v>
+        <v>6.351067800000001</v>
       </c>
       <c r="Q31">
-        <v>6.904455540000001</v>
+        <v>6.888067800000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2130752374114058</v>
+        <v>0.2152901515451451</v>
       </c>
       <c r="T31">
-        <v>1.023034528796835</v>
+        <v>1.036580667915816</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>14.39827410087011</v>
+        <v>13.91833163084111</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3848,22 +3848,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1642841060816016</v>
+        <v>0.1641564936011051</v>
       </c>
       <c r="C32">
-        <v>26.50966872943911</v>
+        <v>26.18796086700418</v>
       </c>
       <c r="D32">
-        <v>37.36966872943911</v>
+        <v>37.40996086700418</v>
       </c>
       <c r="E32">
-        <v>10.86</v>
+        <v>11.222</v>
       </c>
       <c r="F32">
-        <v>10.86</v>
+        <v>11.222</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3884,28 +3884,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M32">
-        <v>0.546258</v>
+        <v>0.5644666</v>
       </c>
       <c r="N32">
-        <v>7.056742000000001</v>
+        <v>7.0385334</v>
       </c>
       <c r="O32">
-        <v>0.7056742000000001</v>
+        <v>0.7038533400000001</v>
       </c>
       <c r="P32">
-        <v>6.351067800000001</v>
+        <v>6.33468006</v>
       </c>
       <c r="Q32">
-        <v>6.888067800000001</v>
+        <v>6.87168006</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2152901515451451</v>
+        <v>0.2175692660885581</v>
       </c>
       <c r="T32">
-        <v>1.036580667915816</v>
+        <v>1.050519448748391</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.91833163084111</v>
+        <v>13.46935319113655</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3930,22 +3930,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1641564936011051</v>
+        <v>0.1640288811206086</v>
       </c>
       <c r="C33">
-        <v>26.18796086700418</v>
+        <v>25.86633998466365</v>
       </c>
       <c r="D33">
-        <v>37.40996086700418</v>
+        <v>37.45033998466365</v>
       </c>
       <c r="E33">
-        <v>11.222</v>
+        <v>11.584</v>
       </c>
       <c r="F33">
-        <v>11.222</v>
+        <v>11.584</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3966,28 +3966,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M33">
-        <v>0.5644666</v>
+        <v>0.5826752000000001</v>
       </c>
       <c r="N33">
-        <v>7.0385334</v>
+        <v>7.020324800000001</v>
       </c>
       <c r="O33">
-        <v>0.7038533400000001</v>
+        <v>0.7020324800000002</v>
       </c>
       <c r="P33">
-        <v>6.33468006</v>
+        <v>6.318292320000001</v>
       </c>
       <c r="Q33">
-        <v>6.87168006</v>
+        <v>6.855292320000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2175692660885581</v>
+        <v>0.2199154134126597</v>
       </c>
       <c r="T33">
-        <v>1.050519448748391</v>
+        <v>1.0648681937231</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>13.46935319113655</v>
+        <v>13.04843590391354</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4012,22 +4012,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1640288811206086</v>
+        <v>0.1643467686401121</v>
       </c>
       <c r="C34">
-        <v>25.86633998466365</v>
+        <v>25.40391552080981</v>
       </c>
       <c r="D34">
-        <v>37.45033998466365</v>
+        <v>37.34991552080982</v>
       </c>
       <c r="E34">
-        <v>11.584</v>
+        <v>11.946</v>
       </c>
       <c r="F34">
-        <v>11.584</v>
+        <v>11.946</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4048,45 +4048,45 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M34">
-        <v>0.5826752000000001</v>
+        <v>0.6188028000000001</v>
       </c>
       <c r="N34">
-        <v>7.020324800000001</v>
+        <v>6.984197200000001</v>
       </c>
       <c r="O34">
-        <v>0.7020324800000002</v>
+        <v>0.6984197200000001</v>
       </c>
       <c r="P34">
-        <v>6.318292320000001</v>
+        <v>6.28577748</v>
       </c>
       <c r="Q34">
-        <v>6.855292320000001</v>
+        <v>6.82277748</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2199154134126597</v>
+        <v>0.222331594985242</v>
       </c>
       <c r="T34">
-        <v>1.0648681937231</v>
+        <v>1.079645259443323</v>
       </c>
       <c r="U34">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V34">
         <v>0.1</v>
       </c>
       <c r="W34">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y34">
-        <v>13.04843590391354</v>
+        <v>12.28662830872775</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4094,22 +4094,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1643467686401121</v>
+        <v>0.1642326561596156</v>
       </c>
       <c r="C35">
-        <v>25.40391552080981</v>
+        <v>25.07790298950822</v>
       </c>
       <c r="D35">
-        <v>37.34991552080982</v>
+        <v>37.38590298950822</v>
       </c>
       <c r="E35">
-        <v>11.946</v>
+        <v>12.308</v>
       </c>
       <c r="F35">
-        <v>11.946</v>
+        <v>12.308</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4130,28 +4130,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M35">
-        <v>0.6188028000000001</v>
+        <v>0.6375544000000001</v>
       </c>
       <c r="N35">
-        <v>6.984197200000001</v>
+        <v>6.965445600000001</v>
       </c>
       <c r="O35">
-        <v>0.6984197200000001</v>
+        <v>0.6965445600000001</v>
       </c>
       <c r="P35">
-        <v>6.28577748</v>
+        <v>6.26890104</v>
       </c>
       <c r="Q35">
-        <v>6.82277748</v>
+        <v>6.80590104</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.222331594985242</v>
+        <v>0.2248209941812358</v>
       </c>
       <c r="T35">
-        <v>1.079645259443323</v>
+        <v>1.094870115033857</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>12.28662830872775</v>
+        <v>11.92525688788282</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4176,22 +4176,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1642326561596156</v>
+        <v>0.1641185436791191</v>
       </c>
       <c r="C36">
-        <v>25.07790298950822</v>
+        <v>24.75195987453298</v>
       </c>
       <c r="D36">
-        <v>37.38590298950822</v>
+        <v>37.42195987453298</v>
       </c>
       <c r="E36">
-        <v>12.308</v>
+        <v>12.67</v>
       </c>
       <c r="F36">
-        <v>12.308</v>
+        <v>12.67</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4212,28 +4212,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M36">
-        <v>0.6375544000000001</v>
+        <v>0.6563060000000001</v>
       </c>
       <c r="N36">
-        <v>6.965445600000001</v>
+        <v>6.946694000000001</v>
       </c>
       <c r="O36">
-        <v>0.6965445600000001</v>
+        <v>0.6946694000000001</v>
       </c>
       <c r="P36">
-        <v>6.26890104</v>
+        <v>6.2520246</v>
       </c>
       <c r="Q36">
-        <v>6.80590104</v>
+        <v>6.7890246</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2248209941812358</v>
+        <v>0.2273869902755679</v>
       </c>
       <c r="T36">
-        <v>1.094870115033857</v>
+        <v>1.110563427719483</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.92525688788282</v>
+        <v>11.58453526251474</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4258,22 +4258,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1641185436791191</v>
+        <v>0.1640044311986226</v>
       </c>
       <c r="C37">
-        <v>24.75195987453298</v>
+        <v>24.42608637692397</v>
       </c>
       <c r="D37">
-        <v>37.42195987453298</v>
+        <v>37.45808637692397</v>
       </c>
       <c r="E37">
-        <v>12.67</v>
+        <v>13.032</v>
       </c>
       <c r="F37">
-        <v>12.67</v>
+        <v>13.032</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4294,28 +4294,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M37">
-        <v>0.6563060000000001</v>
+        <v>0.6750576</v>
       </c>
       <c r="N37">
-        <v>6.946694000000001</v>
+        <v>6.927942400000001</v>
       </c>
       <c r="O37">
-        <v>0.6946694000000001</v>
+        <v>0.6927942400000001</v>
       </c>
       <c r="P37">
-        <v>6.2520246</v>
+        <v>6.23514816</v>
       </c>
       <c r="Q37">
-        <v>6.7890246</v>
+        <v>6.77214816</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2273869902755679</v>
+        <v>0.2300331737478479</v>
       </c>
       <c r="T37">
-        <v>1.110563427719483</v>
+        <v>1.126747156426535</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.58453526251474</v>
+        <v>11.26274261633378</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4340,22 +4340,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1640044311986227</v>
+        <v>0.1638903187181261</v>
       </c>
       <c r="C38">
-        <v>24.42608637692397</v>
+        <v>24.10028269849819</v>
       </c>
       <c r="D38">
-        <v>37.45808637692397</v>
+        <v>37.49428269849819</v>
       </c>
       <c r="E38">
-        <v>13.032</v>
+        <v>13.394</v>
       </c>
       <c r="F38">
-        <v>13.032</v>
+        <v>13.394</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4376,28 +4376,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M38">
-        <v>0.6750576</v>
+        <v>0.6938092</v>
       </c>
       <c r="N38">
-        <v>6.927942400000001</v>
+        <v>6.909190800000001</v>
       </c>
       <c r="O38">
-        <v>0.6927942400000001</v>
+        <v>0.6909190800000001</v>
       </c>
       <c r="P38">
-        <v>6.23514816</v>
+        <v>6.218271720000001</v>
       </c>
       <c r="Q38">
-        <v>6.77214816</v>
+        <v>6.755271720000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2300331737478479</v>
+        <v>0.2327633630446446</v>
       </c>
       <c r="T38">
-        <v>1.126747156426535</v>
+        <v>1.14344465429889</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.26274261633378</v>
+        <v>10.95834416724368</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4422,22 +4422,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1638903187181261</v>
+        <v>0.1637762062376296</v>
       </c>
       <c r="C39">
-        <v>24.10028269849819</v>
+        <v>23.77454904185343</v>
       </c>
       <c r="D39">
-        <v>37.49428269849819</v>
+        <v>37.53054904185343</v>
       </c>
       <c r="E39">
-        <v>13.394</v>
+        <v>13.756</v>
       </c>
       <c r="F39">
-        <v>13.394</v>
+        <v>13.756</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4458,28 +4458,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M39">
-        <v>0.6938092</v>
+        <v>0.7125608000000001</v>
       </c>
       <c r="N39">
-        <v>6.909190800000001</v>
+        <v>6.8904392</v>
       </c>
       <c r="O39">
-        <v>0.6909190800000001</v>
+        <v>0.68904392</v>
       </c>
       <c r="P39">
-        <v>6.218271720000001</v>
+        <v>6.20139528</v>
       </c>
       <c r="Q39">
-        <v>6.755271720000001</v>
+        <v>6.73839528</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2327633630446446</v>
+        <v>0.2355816229639188</v>
       </c>
       <c r="T39">
-        <v>1.14344465429889</v>
+        <v>1.16068078113487</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.95834416724368</v>
+        <v>10.66996668915831</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4504,22 +4504,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1637762062376296</v>
+        <v>0.1636620937571331</v>
       </c>
       <c r="C40">
-        <v>23.77454904185343</v>
+        <v>23.44888561037211</v>
       </c>
       <c r="D40">
-        <v>37.53054904185343</v>
+        <v>37.56688561037211</v>
       </c>
       <c r="E40">
-        <v>13.756</v>
+        <v>14.118</v>
       </c>
       <c r="F40">
-        <v>13.756</v>
+        <v>14.118</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4540,28 +4540,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M40">
-        <v>0.7125608000000001</v>
+        <v>0.7313124000000001</v>
       </c>
       <c r="N40">
-        <v>6.8904392</v>
+        <v>6.8716876</v>
       </c>
       <c r="O40">
-        <v>0.68904392</v>
+        <v>0.68716876</v>
       </c>
       <c r="P40">
-        <v>6.20139528</v>
+        <v>6.184518840000001</v>
       </c>
       <c r="Q40">
-        <v>6.73839528</v>
+        <v>6.721518840000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2355816229639188</v>
+        <v>0.2384922848477593</v>
       </c>
       <c r="T40">
-        <v>1.16068078113487</v>
+        <v>1.178482026883504</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.66996668915831</v>
+        <v>10.39637779969272</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4586,22 +4586,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1636620937571331</v>
+        <v>0.1635479812766366</v>
       </c>
       <c r="C41">
-        <v>23.44888561037211</v>
+        <v>23.12329260822506</v>
       </c>
       <c r="D41">
-        <v>37.56688561037211</v>
+        <v>37.60329260822506</v>
       </c>
       <c r="E41">
-        <v>14.118</v>
+        <v>14.48</v>
       </c>
       <c r="F41">
-        <v>14.118</v>
+        <v>14.48</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4622,28 +4622,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M41">
-        <v>0.7313124000000001</v>
+        <v>0.7500640000000001</v>
       </c>
       <c r="N41">
-        <v>6.8716876</v>
+        <v>6.852936000000001</v>
       </c>
       <c r="O41">
-        <v>0.68716876</v>
+        <v>0.6852936000000001</v>
       </c>
       <c r="P41">
-        <v>6.184518840000001</v>
+        <v>6.1676424</v>
       </c>
       <c r="Q41">
-        <v>6.721518840000001</v>
+        <v>6.7046424</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2384922848477593</v>
+        <v>0.2414999687943944</v>
       </c>
       <c r="T41">
-        <v>1.178482026883504</v>
+        <v>1.196876647490427</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.39637779969272</v>
+        <v>10.1364683547004</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4668,22 +4668,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1635479812766366</v>
+        <v>0.1634338687961401</v>
       </c>
       <c r="C42">
-        <v>23.12329260822506</v>
+        <v>22.79777024037534</v>
       </c>
       <c r="D42">
-        <v>37.60329260822506</v>
+        <v>37.63977024037534</v>
       </c>
       <c r="E42">
-        <v>14.48</v>
+        <v>14.842</v>
       </c>
       <c r="F42">
-        <v>14.48</v>
+        <v>14.842</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4704,28 +4704,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M42">
-        <v>0.7500640000000001</v>
+        <v>0.7688156000000002</v>
       </c>
       <c r="N42">
-        <v>6.852936000000001</v>
+        <v>6.834184400000001</v>
       </c>
       <c r="O42">
-        <v>0.6852936000000001</v>
+        <v>0.6834184400000001</v>
       </c>
       <c r="P42">
-        <v>6.1676424</v>
+        <v>6.150765960000001</v>
       </c>
       <c r="Q42">
-        <v>6.7046424</v>
+        <v>6.687765960000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2414999687943944</v>
+        <v>0.2446096081290511</v>
       </c>
       <c r="T42">
-        <v>1.196876647490427</v>
+        <v>1.215894814558601</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.1364683547004</v>
+        <v>9.889237419219901</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4750,22 +4750,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1634338687961401</v>
+        <v>0.1639623563156436</v>
       </c>
       <c r="C43">
-        <v>22.79777024037534</v>
+        <v>22.26742433539119</v>
       </c>
       <c r="D43">
-        <v>37.63977024037534</v>
+        <v>37.47142433539119</v>
       </c>
       <c r="E43">
-        <v>14.842</v>
+        <v>15.204</v>
       </c>
       <c r="F43">
-        <v>14.842</v>
+        <v>15.204</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4786,45 +4786,45 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M43">
-        <v>0.7688156000000002</v>
+        <v>0.8134140000000001</v>
       </c>
       <c r="N43">
-        <v>6.834184400000001</v>
+        <v>6.789586000000001</v>
       </c>
       <c r="O43">
-        <v>0.6834184400000001</v>
+        <v>0.6789586000000001</v>
       </c>
       <c r="P43">
-        <v>6.150765960000001</v>
+        <v>6.1106274</v>
       </c>
       <c r="Q43">
-        <v>6.687765960000001</v>
+        <v>6.6476274</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2446096081290511</v>
+        <v>0.2478264764062822</v>
       </c>
       <c r="T43">
-        <v>1.215894814558601</v>
+        <v>1.235568780491195</v>
       </c>
       <c r="U43">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V43">
         <v>0.1</v>
       </c>
       <c r="W43">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>9.889237419219901</v>
+        <v>9.347023778789152</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4832,22 +4832,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1639623563156437</v>
+        <v>0.1638635438351472</v>
       </c>
       <c r="C44">
-        <v>22.26742433539118</v>
+        <v>21.93678578928321</v>
       </c>
       <c r="D44">
-        <v>37.47142433539118</v>
+        <v>37.50278578928322</v>
       </c>
       <c r="E44">
-        <v>15.204</v>
+        <v>15.566</v>
       </c>
       <c r="F44">
-        <v>15.204</v>
+        <v>15.566</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4868,28 +4868,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M44">
-        <v>0.813414</v>
+        <v>0.832781</v>
       </c>
       <c r="N44">
-        <v>6.789586000000001</v>
+        <v>6.770219000000001</v>
       </c>
       <c r="O44">
-        <v>0.6789586000000001</v>
+        <v>0.6770219000000002</v>
       </c>
       <c r="P44">
-        <v>6.1106274</v>
+        <v>6.093197100000001</v>
       </c>
       <c r="Q44">
-        <v>6.6476274</v>
+        <v>6.630197100000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2478264764062822</v>
+        <v>0.2511562172546441</v>
       </c>
       <c r="T44">
-        <v>1.235568780491195</v>
+        <v>1.255933061017915</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.347023778789154</v>
+        <v>9.129651132770801</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4914,22 +4914,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1638635438351472</v>
+        <v>0.1637647313546507</v>
       </c>
       <c r="C45">
-        <v>21.93678578928321</v>
+        <v>21.60619978265913</v>
       </c>
       <c r="D45">
-        <v>37.50278578928322</v>
+        <v>37.53419978265913</v>
       </c>
       <c r="E45">
-        <v>15.566</v>
+        <v>15.928</v>
       </c>
       <c r="F45">
-        <v>15.566</v>
+        <v>15.928</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4950,28 +4950,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M45">
-        <v>0.832781</v>
+        <v>0.852148</v>
       </c>
       <c r="N45">
-        <v>6.770219000000001</v>
+        <v>6.750852000000001</v>
       </c>
       <c r="O45">
-        <v>0.6770219000000002</v>
+        <v>0.6750852000000002</v>
       </c>
       <c r="P45">
-        <v>6.093197100000001</v>
+        <v>6.075766800000001</v>
       </c>
       <c r="Q45">
-        <v>6.630197100000001</v>
+        <v>6.612766800000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2511562172546441</v>
+        <v>0.254604877419019</v>
       </c>
       <c r="T45">
-        <v>1.255933061017915</v>
+        <v>1.277024637277733</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>9.129651132770801</v>
+        <v>8.922159061571465</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4996,22 +4996,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1637647313546507</v>
+        <v>0.1636659188741542</v>
       </c>
       <c r="C46">
-        <v>21.60619978265913</v>
+        <v>21.27566644765783</v>
       </c>
       <c r="D46">
-        <v>37.53419978265913</v>
+        <v>37.56566644765783</v>
       </c>
       <c r="E46">
-        <v>15.928</v>
+        <v>16.29</v>
       </c>
       <c r="F46">
-        <v>15.928</v>
+        <v>16.29</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5032,28 +5032,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M46">
-        <v>0.852148</v>
+        <v>0.8715150000000002</v>
       </c>
       <c r="N46">
-        <v>6.750852000000001</v>
+        <v>6.731485</v>
       </c>
       <c r="O46">
-        <v>0.6750852000000002</v>
+        <v>0.6731485</v>
       </c>
       <c r="P46">
-        <v>6.075766800000001</v>
+        <v>6.0583365</v>
       </c>
       <c r="Q46">
-        <v>6.612766800000001</v>
+        <v>6.5953365</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.254604877419019</v>
+        <v>0.258178943407553</v>
       </c>
       <c r="T46">
-        <v>1.277024637277733</v>
+        <v>1.298883179946997</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.922159061571465</v>
+        <v>8.723888860203207</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5078,22 +5078,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1636659188741542</v>
+        <v>0.1635671063936577</v>
       </c>
       <c r="C47">
-        <v>21.27566644765783</v>
+        <v>20.94518591686165</v>
       </c>
       <c r="D47">
-        <v>37.56566644765783</v>
+        <v>37.59718591686165</v>
       </c>
       <c r="E47">
-        <v>16.29</v>
+        <v>16.652</v>
       </c>
       <c r="F47">
-        <v>16.29</v>
+        <v>16.652</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5114,28 +5114,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M47">
-        <v>0.8715150000000002</v>
+        <v>0.8908820000000001</v>
       </c>
       <c r="N47">
-        <v>6.731485</v>
+        <v>6.712118</v>
       </c>
       <c r="O47">
-        <v>0.6731485</v>
+        <v>0.6712118</v>
       </c>
       <c r="P47">
-        <v>6.0583365</v>
+        <v>6.0409062</v>
       </c>
       <c r="Q47">
-        <v>6.5953365</v>
+        <v>6.5779062</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.258178943407553</v>
+        <v>0.2618853822104771</v>
       </c>
       <c r="T47">
-        <v>1.298883179946997</v>
+        <v>1.32155129827068</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.723888860203207</v>
+        <v>8.534239102372705</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5160,22 +5160,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1635671063936577</v>
+        <v>0.1634682939131612</v>
       </c>
       <c r="C48">
-        <v>20.94518591686165</v>
+        <v>20.61475832329829</v>
       </c>
       <c r="D48">
-        <v>37.59718591686165</v>
+        <v>37.62875832329829</v>
       </c>
       <c r="E48">
-        <v>16.652</v>
+        <v>17.014</v>
       </c>
       <c r="F48">
-        <v>16.652</v>
+        <v>17.014</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5196,28 +5196,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M48">
-        <v>0.8908820000000001</v>
+        <v>0.9102490000000001</v>
       </c>
       <c r="N48">
-        <v>6.712118</v>
+        <v>6.692751</v>
       </c>
       <c r="O48">
-        <v>0.6712118</v>
+        <v>0.6692751000000001</v>
       </c>
       <c r="P48">
-        <v>6.0409062</v>
+        <v>6.0234759</v>
       </c>
       <c r="Q48">
-        <v>6.5779062</v>
+        <v>6.5604759</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2618853822104771</v>
+        <v>0.265731686628606</v>
       </c>
       <c r="T48">
-        <v>1.32155129827068</v>
+        <v>1.345074817285822</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.534239102372705</v>
+        <v>8.352659547003071</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5242,22 +5242,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1634682939131612</v>
+        <v>0.1633694814326647</v>
       </c>
       <c r="C49">
-        <v>20.61475832329829</v>
+        <v>20.28438380044269</v>
       </c>
       <c r="D49">
-        <v>37.62875832329829</v>
+        <v>37.66038380044269</v>
       </c>
       <c r="E49">
-        <v>17.014</v>
+        <v>17.376</v>
       </c>
       <c r="F49">
-        <v>17.014</v>
+        <v>17.376</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5278,28 +5278,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M49">
-        <v>0.9102490000000001</v>
+        <v>0.929616</v>
       </c>
       <c r="N49">
-        <v>6.692751</v>
+        <v>6.673384</v>
       </c>
       <c r="O49">
-        <v>0.6692751000000001</v>
+        <v>0.6673384000000001</v>
       </c>
       <c r="P49">
-        <v>6.0234759</v>
+        <v>6.0060456</v>
       </c>
       <c r="Q49">
-        <v>6.5604759</v>
+        <v>6.5430456</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.265731686628606</v>
+        <v>0.2697259258320475</v>
       </c>
       <c r="T49">
-        <v>1.345074817285822</v>
+        <v>1.369503087032315</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.352659547003071</v>
+        <v>8.17864580644051</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5324,22 +5324,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1633694814326646</v>
+        <v>0.1632706689521682</v>
       </c>
       <c r="C50">
-        <v>20.28438380044271</v>
+        <v>19.95406248221889</v>
       </c>
       <c r="D50">
-        <v>37.66038380044272</v>
+        <v>37.69206248221889</v>
       </c>
       <c r="E50">
-        <v>17.376</v>
+        <v>17.738</v>
       </c>
       <c r="F50">
-        <v>17.376</v>
+        <v>17.738</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5360,28 +5360,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M50">
-        <v>0.929616</v>
+        <v>0.9489829999999999</v>
       </c>
       <c r="N50">
-        <v>6.673384</v>
+        <v>6.654017000000001</v>
       </c>
       <c r="O50">
-        <v>0.6673384000000001</v>
+        <v>0.6654017000000001</v>
       </c>
       <c r="P50">
-        <v>6.0060456</v>
+        <v>5.9886153</v>
       </c>
       <c r="Q50">
-        <v>6.5430456</v>
+        <v>6.5256153</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2697259258320474</v>
+        <v>0.2738768018669964</v>
       </c>
       <c r="T50">
-        <v>1.369503087032315</v>
+        <v>1.394889328141417</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.17864580644051</v>
+        <v>8.01173466753356</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5406,22 +5406,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1632706689521682</v>
+        <v>0.1631718564716717</v>
       </c>
       <c r="C51">
-        <v>19.95406248221889</v>
+        <v>19.62379450300189</v>
       </c>
       <c r="D51">
-        <v>37.69206248221889</v>
+        <v>37.72379450300189</v>
       </c>
       <c r="E51">
-        <v>17.738</v>
+        <v>18.1</v>
       </c>
       <c r="F51">
-        <v>17.738</v>
+        <v>18.1</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5442,28 +5442,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M51">
-        <v>0.9489829999999999</v>
+        <v>0.96835</v>
       </c>
       <c r="N51">
-        <v>6.654017000000001</v>
+        <v>6.634650000000001</v>
       </c>
       <c r="O51">
-        <v>0.6654017000000001</v>
+        <v>0.6634650000000001</v>
       </c>
       <c r="P51">
-        <v>5.9886153</v>
+        <v>5.971185</v>
       </c>
       <c r="Q51">
-        <v>6.5256153</v>
+        <v>6.508185</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2738768018669964</v>
+        <v>0.2781937129433433</v>
       </c>
       <c r="T51">
-        <v>1.394889328141417</v>
+        <v>1.421291018894882</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.01173466753356</v>
+        <v>7.851499974182889</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5488,22 +5488,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1631718564716717</v>
+        <v>0.1630730439911752</v>
       </c>
       <c r="C52">
-        <v>19.62379450300189</v>
+        <v>19.29357999761957</v>
       </c>
       <c r="D52">
-        <v>37.72379450300189</v>
+        <v>37.75557999761958</v>
       </c>
       <c r="E52">
-        <v>18.1</v>
+        <v>18.462</v>
       </c>
       <c r="F52">
-        <v>18.1</v>
+        <v>18.462</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5524,28 +5524,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M52">
-        <v>0.96835</v>
+        <v>0.9877170000000002</v>
       </c>
       <c r="N52">
-        <v>6.634650000000001</v>
+        <v>6.615283000000001</v>
       </c>
       <c r="O52">
-        <v>0.6634650000000001</v>
+        <v>0.6615283000000001</v>
       </c>
       <c r="P52">
-        <v>5.971185</v>
+        <v>5.953754700000001</v>
       </c>
       <c r="Q52">
-        <v>6.508185</v>
+        <v>6.490754700000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2781937129433433</v>
+        <v>0.2826868244717861</v>
       </c>
       <c r="T52">
-        <v>1.421291018894882</v>
+        <v>1.448770329679101</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.851499974182889</v>
+        <v>7.697548994296949</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5570,22 +5570,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1630730439911752</v>
+        <v>0.1633486315106787</v>
       </c>
       <c r="C53">
-        <v>19.29357999761957</v>
+        <v>18.84306372562865</v>
       </c>
       <c r="D53">
-        <v>37.75557999761958</v>
+        <v>37.66706372562865</v>
       </c>
       <c r="E53">
-        <v>18.462</v>
+        <v>18.824</v>
       </c>
       <c r="F53">
-        <v>18.462</v>
+        <v>18.824</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5606,45 +5606,45 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M53">
-        <v>0.9877170000000002</v>
+        <v>1.0221432</v>
       </c>
       <c r="N53">
-        <v>6.615283000000001</v>
+        <v>6.5808568</v>
       </c>
       <c r="O53">
-        <v>0.6615283000000001</v>
+        <v>0.6580856800000001</v>
       </c>
       <c r="P53">
-        <v>5.953754700000001</v>
+        <v>5.92277112</v>
       </c>
       <c r="Q53">
-        <v>6.490754700000001</v>
+        <v>6.45977112</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2826868244717861</v>
+        <v>0.2873671489805806</v>
       </c>
       <c r="T53">
-        <v>1.448770329679101</v>
+        <v>1.477394611745996</v>
       </c>
       <c r="U53">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V53">
         <v>0.1</v>
       </c>
       <c r="W53">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y53">
-        <v>7.697548994296949</v>
+        <v>7.438292403647551</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5652,22 +5652,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1633486315106787</v>
+        <v>0.1632570190301822</v>
       </c>
       <c r="C54">
-        <v>18.84306372562865</v>
+        <v>18.51044275439523</v>
       </c>
       <c r="D54">
-        <v>37.66706372562865</v>
+        <v>37.69644275439524</v>
       </c>
       <c r="E54">
-        <v>18.824</v>
+        <v>19.186</v>
       </c>
       <c r="F54">
-        <v>18.824</v>
+        <v>19.186</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5688,28 +5688,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M54">
-        <v>1.0221432</v>
+        <v>1.0417998</v>
       </c>
       <c r="N54">
-        <v>6.5808568</v>
+        <v>6.5612002</v>
       </c>
       <c r="O54">
-        <v>0.6580856800000001</v>
+        <v>0.65612002</v>
       </c>
       <c r="P54">
-        <v>5.92277112</v>
+        <v>5.90508018</v>
       </c>
       <c r="Q54">
-        <v>6.45977112</v>
+        <v>6.44208018</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2873671489805806</v>
+        <v>0.2922466362344301</v>
       </c>
       <c r="T54">
-        <v>1.477394611745996</v>
+        <v>1.507236948368929</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.438292403647551</v>
+        <v>7.297947263956087</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5734,22 +5734,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1632570190301822</v>
+        <v>0.1631654065496857</v>
       </c>
       <c r="C55">
-        <v>18.51044275439523</v>
+        <v>18.17786764822169</v>
       </c>
       <c r="D55">
-        <v>37.69644275439524</v>
+        <v>37.72586764822169</v>
       </c>
       <c r="E55">
-        <v>19.186</v>
+        <v>19.548</v>
       </c>
       <c r="F55">
-        <v>19.186</v>
+        <v>19.548</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5770,28 +5770,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M55">
-        <v>1.0417998</v>
+        <v>1.0614564</v>
       </c>
       <c r="N55">
-        <v>6.5612002</v>
+        <v>6.541543600000001</v>
       </c>
       <c r="O55">
-        <v>0.65612002</v>
+        <v>0.6541543600000002</v>
       </c>
       <c r="P55">
-        <v>5.90508018</v>
+        <v>5.887389240000001</v>
       </c>
       <c r="Q55">
-        <v>6.44208018</v>
+        <v>6.424389240000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2922466362344301</v>
+        <v>0.2973382751080124</v>
       </c>
       <c r="T55">
-        <v>1.507236948368929</v>
+        <v>1.538376777888511</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.297947263956087</v>
+        <v>7.162800092401345</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5816,22 +5816,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1631654065496857</v>
+        <v>0.1630737940691892</v>
       </c>
       <c r="C56">
-        <v>18.17786764822169</v>
+        <v>17.84533851459526</v>
       </c>
       <c r="D56">
-        <v>37.72586764822169</v>
+        <v>37.75533851459527</v>
       </c>
       <c r="E56">
-        <v>19.548</v>
+        <v>19.91</v>
       </c>
       <c r="F56">
-        <v>19.548</v>
+        <v>19.91</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5852,28 +5852,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M56">
-        <v>1.0614564</v>
+        <v>1.081113</v>
       </c>
       <c r="N56">
-        <v>6.541543600000001</v>
+        <v>6.521887</v>
       </c>
       <c r="O56">
-        <v>0.6541543600000002</v>
+        <v>0.6521887000000001</v>
       </c>
       <c r="P56">
-        <v>5.887389240000001</v>
+        <v>5.8696983</v>
       </c>
       <c r="Q56">
-        <v>6.424389240000001</v>
+        <v>6.4066983</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2973382751080124</v>
+        <v>0.3026562090426427</v>
       </c>
       <c r="T56">
-        <v>1.538376777888511</v>
+        <v>1.570900599831186</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.162800092401345</v>
+        <v>7.032567363448593</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5898,22 +5898,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1630737940691892</v>
+        <v>0.1629821815886927</v>
       </c>
       <c r="C57">
-        <v>17.84533851459526</v>
+        <v>17.51285546133933</v>
       </c>
       <c r="D57">
-        <v>37.75533851459527</v>
+        <v>37.78485546133933</v>
       </c>
       <c r="E57">
-        <v>19.91</v>
+        <v>20.272</v>
       </c>
       <c r="F57">
-        <v>19.91</v>
+        <v>20.272</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5934,28 +5934,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M57">
-        <v>1.081113</v>
+        <v>1.1007696</v>
       </c>
       <c r="N57">
-        <v>6.521887</v>
+        <v>6.5022304</v>
       </c>
       <c r="O57">
-        <v>0.6521887000000001</v>
+        <v>0.6502230400000001</v>
       </c>
       <c r="P57">
-        <v>5.8696983</v>
+        <v>5.85200736</v>
       </c>
       <c r="Q57">
-        <v>6.4066983</v>
+        <v>6.38900736</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3026562090426427</v>
+        <v>0.3082158672470289</v>
       </c>
       <c r="T57">
-        <v>1.570900599831186</v>
+        <v>1.604902777316709</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.032567363448593</v>
+        <v>6.906985803387011</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5980,22 +5980,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1629821815886927</v>
+        <v>0.1628905691081962</v>
       </c>
       <c r="C58">
-        <v>17.51285546133933</v>
+        <v>17.18041859661469</v>
       </c>
       <c r="D58">
-        <v>37.78485546133933</v>
+        <v>37.81441859661469</v>
       </c>
       <c r="E58">
-        <v>20.272</v>
+        <v>20.634</v>
       </c>
       <c r="F58">
-        <v>20.272</v>
+        <v>20.634</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6016,28 +6016,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M58">
-        <v>1.1007696</v>
+        <v>1.1204262</v>
       </c>
       <c r="N58">
-        <v>6.5022304</v>
+        <v>6.482573800000001</v>
       </c>
       <c r="O58">
-        <v>0.6502230400000001</v>
+        <v>0.6482573800000001</v>
       </c>
       <c r="P58">
-        <v>5.85200736</v>
+        <v>5.83431642</v>
       </c>
       <c r="Q58">
-        <v>6.38900736</v>
+        <v>6.37131642</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3082158672470289</v>
+        <v>0.3140341142051075</v>
       </c>
       <c r="T58">
-        <v>1.604902777316709</v>
+        <v>1.640486451429466</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.906985803387011</v>
+        <v>6.785810613853906</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6062,22 +6062,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1628905691081962</v>
+        <v>0.1627989566276997</v>
       </c>
       <c r="C59">
-        <v>17.18041859661469</v>
+        <v>16.84802802892093</v>
       </c>
       <c r="D59">
-        <v>37.81441859661469</v>
+        <v>37.84402802892094</v>
       </c>
       <c r="E59">
-        <v>20.634</v>
+        <v>20.99600000000001</v>
       </c>
       <c r="F59">
-        <v>20.634</v>
+        <v>20.99600000000001</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6098,28 +6098,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M59">
-        <v>1.1204262</v>
+        <v>1.1400828</v>
       </c>
       <c r="N59">
-        <v>6.482573800000001</v>
+        <v>6.462917200000001</v>
       </c>
       <c r="O59">
-        <v>0.6482573800000001</v>
+        <v>0.6462917200000001</v>
       </c>
       <c r="P59">
-        <v>5.83431642</v>
+        <v>5.816625480000001</v>
       </c>
       <c r="Q59">
-        <v>6.37131642</v>
+        <v>6.353625480000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3140341142051075</v>
+        <v>0.3201294205421422</v>
       </c>
       <c r="T59">
-        <v>1.640486451429466</v>
+        <v>1.67776458621426</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.785810613853906</v>
+        <v>6.668813879132287</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6144,22 +6144,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1627989566276997</v>
+        <v>0.1627073441472032</v>
       </c>
       <c r="C60">
-        <v>16.84802802892094</v>
+        <v>16.51568386709773</v>
       </c>
       <c r="D60">
-        <v>37.84402802892094</v>
+        <v>37.87368386709773</v>
       </c>
       <c r="E60">
-        <v>20.996</v>
+        <v>21.358</v>
       </c>
       <c r="F60">
-        <v>20.996</v>
+        <v>21.358</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6180,28 +6180,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M60">
-        <v>1.1400828</v>
+        <v>1.1597394</v>
       </c>
       <c r="N60">
-        <v>6.462917200000001</v>
+        <v>6.4432606</v>
       </c>
       <c r="O60">
-        <v>0.6462917200000001</v>
+        <v>0.64432606</v>
       </c>
       <c r="P60">
-        <v>5.816625480000001</v>
+        <v>5.79893454</v>
       </c>
       <c r="Q60">
-        <v>6.353625480000001</v>
+        <v>6.33593454</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3201294205421422</v>
+        <v>0.3265220588956176</v>
       </c>
       <c r="T60">
-        <v>1.677764586214259</v>
+        <v>1.71686116659831</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.668813879132289</v>
+        <v>6.555783135418181</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6226,22 +6226,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1627073441472032</v>
+        <v>0.1626157316667067</v>
       </c>
       <c r="C61">
-        <v>16.51568386709773</v>
+        <v>16.18338622032619</v>
       </c>
       <c r="D61">
-        <v>37.87368386709773</v>
+        <v>37.90338622032619</v>
       </c>
       <c r="E61">
-        <v>21.358</v>
+        <v>21.72</v>
       </c>
       <c r="F61">
-        <v>21.358</v>
+        <v>21.72</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6262,28 +6262,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M61">
-        <v>1.1597394</v>
+        <v>1.179396</v>
       </c>
       <c r="N61">
-        <v>6.4432606</v>
+        <v>6.423604000000001</v>
       </c>
       <c r="O61">
-        <v>0.64432606</v>
+        <v>0.6423604000000002</v>
       </c>
       <c r="P61">
-        <v>5.79893454</v>
+        <v>5.781243600000001</v>
       </c>
       <c r="Q61">
-        <v>6.33593454</v>
+        <v>6.318243600000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3265220588956176</v>
+        <v>0.3332343291667668</v>
       </c>
       <c r="T61">
-        <v>1.71686116659831</v>
+        <v>1.757912576001564</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.555783135418181</v>
+        <v>6.446520083161212</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6308,22 +6308,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1626157316667067</v>
+        <v>0.1625241191862102</v>
       </c>
       <c r="C62">
-        <v>16.18338622032619</v>
+        <v>15.85113519813018</v>
       </c>
       <c r="D62">
-        <v>37.90338622032619</v>
+        <v>37.93313519813018</v>
       </c>
       <c r="E62">
-        <v>21.72</v>
+        <v>22.082</v>
       </c>
       <c r="F62">
-        <v>21.72</v>
+        <v>22.082</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6344,28 +6344,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M62">
-        <v>1.179396</v>
+        <v>1.1990526</v>
       </c>
       <c r="N62">
-        <v>6.423604000000001</v>
+        <v>6.403947400000001</v>
       </c>
       <c r="O62">
-        <v>0.6423604000000002</v>
+        <v>0.6403947400000001</v>
       </c>
       <c r="P62">
-        <v>5.781243600000001</v>
+        <v>5.76355266</v>
       </c>
       <c r="Q62">
-        <v>6.318243600000001</v>
+        <v>6.30055266</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3332343291667668</v>
+        <v>0.3402908184261801</v>
       </c>
       <c r="T62">
-        <v>1.757912576001564</v>
+        <v>1.801069185887037</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.446520083161212</v>
+        <v>6.340839426060207</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6390,22 +6390,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1625241191862102</v>
+        <v>0.1624325067057137</v>
       </c>
       <c r="C63">
-        <v>15.85113519813018</v>
+        <v>15.51893091037769</v>
       </c>
       <c r="D63">
-        <v>37.93313519813018</v>
+        <v>37.96293091037769</v>
       </c>
       <c r="E63">
-        <v>22.082</v>
+        <v>22.444</v>
       </c>
       <c r="F63">
-        <v>22.082</v>
+        <v>22.444</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6426,28 +6426,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M63">
-        <v>1.1990526</v>
+        <v>1.2187092</v>
       </c>
       <c r="N63">
-        <v>6.403947400000001</v>
+        <v>6.3842908</v>
       </c>
       <c r="O63">
-        <v>0.6403947400000001</v>
+        <v>0.6384290800000001</v>
       </c>
       <c r="P63">
-        <v>5.76355266</v>
+        <v>5.745861720000001</v>
       </c>
       <c r="Q63">
-        <v>6.30055266</v>
+        <v>6.282861720000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3402908184261801</v>
+        <v>0.3477187018571414</v>
       </c>
       <c r="T63">
-        <v>1.801069185887037</v>
+        <v>1.846497196292797</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.340839426060207</v>
+        <v>6.238567822414075</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6472,22 +6472,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1624325067057137</v>
+        <v>0.1623408942252172</v>
       </c>
       <c r="C64">
-        <v>15.51893091037769</v>
+        <v>15.1867734672822</v>
       </c>
       <c r="D64">
-        <v>37.96293091037769</v>
+        <v>37.9927734672822</v>
       </c>
       <c r="E64">
-        <v>22.444</v>
+        <v>22.806</v>
       </c>
       <c r="F64">
-        <v>22.444</v>
+        <v>22.806</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6508,28 +6508,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M64">
-        <v>1.2187092</v>
+        <v>1.2383658</v>
       </c>
       <c r="N64">
-        <v>6.3842908</v>
+        <v>6.3646342</v>
       </c>
       <c r="O64">
-        <v>0.6384290800000001</v>
+        <v>0.6364634200000001</v>
       </c>
       <c r="P64">
-        <v>5.745861720000001</v>
+        <v>5.72817078</v>
       </c>
       <c r="Q64">
-        <v>6.282861720000001</v>
+        <v>6.26517078</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3477187018571414</v>
+        <v>0.3555480925005871</v>
       </c>
       <c r="T64">
-        <v>1.846497196292797</v>
+        <v>1.894380774828598</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.238567822414075</v>
+        <v>6.13954293634401</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6554,22 +6554,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1623408942252172</v>
+        <v>0.1628252817447207</v>
       </c>
       <c r="C65">
-        <v>15.1867734672822</v>
+        <v>14.66751492430324</v>
       </c>
       <c r="D65">
-        <v>37.9927734672822</v>
+        <v>37.83551492430325</v>
       </c>
       <c r="E65">
-        <v>22.806</v>
+        <v>23.168</v>
       </c>
       <c r="F65">
-        <v>22.806</v>
+        <v>23.168</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6590,45 +6590,45 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M65">
-        <v>1.2383658</v>
+        <v>1.2811904</v>
       </c>
       <c r="N65">
-        <v>6.3646342</v>
+        <v>6.3218096</v>
       </c>
       <c r="O65">
-        <v>0.6364634200000001</v>
+        <v>0.63218096</v>
       </c>
       <c r="P65">
-        <v>5.72817078</v>
+        <v>5.68962864</v>
       </c>
       <c r="Q65">
-        <v>6.26517078</v>
+        <v>6.226628639999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3555480925005871</v>
+        <v>0.3638124492908909</v>
       </c>
       <c r="T65">
-        <v>1.894380774828598</v>
+        <v>1.944924552171944</v>
       </c>
       <c r="U65">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V65">
         <v>0.1</v>
       </c>
       <c r="W65">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>6.13954293634401</v>
+        <v>5.934324827910043</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6636,22 +6636,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1628252817447207</v>
+        <v>0.1627426692642242</v>
       </c>
       <c r="C66">
-        <v>14.66751492430324</v>
+        <v>14.33224328409206</v>
       </c>
       <c r="D66">
-        <v>37.83551492430325</v>
+        <v>37.86224328409206</v>
       </c>
       <c r="E66">
-        <v>23.168</v>
+        <v>23.53</v>
       </c>
       <c r="F66">
-        <v>23.168</v>
+        <v>23.53</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6672,28 +6672,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M66">
-        <v>1.2811904</v>
+        <v>1.301209</v>
       </c>
       <c r="N66">
-        <v>6.3218096</v>
+        <v>6.301791000000001</v>
       </c>
       <c r="O66">
-        <v>0.63218096</v>
+        <v>0.6301791000000001</v>
       </c>
       <c r="P66">
-        <v>5.68962864</v>
+        <v>5.6716119</v>
       </c>
       <c r="Q66">
-        <v>6.226628639999999</v>
+        <v>6.2086119</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3638124492908909</v>
+        <v>0.3725490550406407</v>
       </c>
       <c r="T66">
-        <v>1.944924552171944</v>
+        <v>1.998356545363481</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.934324827910043</v>
+        <v>5.843027522865274</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6718,22 +6718,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1627426692642242</v>
+        <v>0.1626600567837277</v>
       </c>
       <c r="C67">
-        <v>14.33224328409206</v>
+        <v>13.99700943431437</v>
       </c>
       <c r="D67">
-        <v>37.86224328409206</v>
+        <v>37.88900943431437</v>
       </c>
       <c r="E67">
-        <v>23.53</v>
+        <v>23.892</v>
       </c>
       <c r="F67">
-        <v>23.53</v>
+        <v>23.892</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6754,28 +6754,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M67">
-        <v>1.301209</v>
+        <v>1.3212276</v>
       </c>
       <c r="N67">
-        <v>6.301791000000001</v>
+        <v>6.2817724</v>
       </c>
       <c r="O67">
-        <v>0.6301791000000001</v>
+        <v>0.6281772400000001</v>
       </c>
       <c r="P67">
-        <v>5.6716119</v>
+        <v>5.65359516</v>
       </c>
       <c r="Q67">
-        <v>6.2086119</v>
+        <v>6.19059516</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3725490550406407</v>
+        <v>0.3817995787756698</v>
       </c>
       <c r="T67">
-        <v>1.998356545363481</v>
+        <v>2.054931596978049</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.843027522865274</v>
+        <v>5.75449680282186</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6800,22 +6800,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1626600567837277</v>
+        <v>0.1625774443032313</v>
       </c>
       <c r="C68">
-        <v>13.99700943431437</v>
+        <v>13.66181345517301</v>
       </c>
       <c r="D68">
-        <v>37.88900943431437</v>
+        <v>37.91581345517302</v>
       </c>
       <c r="E68">
-        <v>23.892</v>
+        <v>24.254</v>
       </c>
       <c r="F68">
-        <v>23.892</v>
+        <v>24.254</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6836,28 +6836,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M68">
-        <v>1.3212276</v>
+        <v>1.3412462</v>
       </c>
       <c r="N68">
-        <v>6.2817724</v>
+        <v>6.2617538</v>
       </c>
       <c r="O68">
-        <v>0.6281772400000001</v>
+        <v>0.6261753800000001</v>
       </c>
       <c r="P68">
-        <v>5.65359516</v>
+        <v>5.63557842</v>
       </c>
       <c r="Q68">
-        <v>6.19059516</v>
+        <v>6.17257842</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3817995787756698</v>
+        <v>0.391610740312822</v>
       </c>
       <c r="T68">
-        <v>2.054931596978049</v>
+        <v>2.114935439599562</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.75449680282186</v>
+        <v>5.668608790839444</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6882,22 +6882,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1625774443032313</v>
+        <v>0.1624948318227347</v>
       </c>
       <c r="C69">
-        <v>13.66181345517301</v>
+        <v>13.32665542709799</v>
       </c>
       <c r="D69">
-        <v>37.91581345517302</v>
+        <v>37.94265542709799</v>
       </c>
       <c r="E69">
-        <v>24.254</v>
+        <v>24.616</v>
       </c>
       <c r="F69">
-        <v>24.254</v>
+        <v>24.616</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6918,28 +6918,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M69">
-        <v>1.3412462</v>
+        <v>1.3612648</v>
       </c>
       <c r="N69">
-        <v>6.2617538</v>
+        <v>6.241735200000001</v>
       </c>
       <c r="O69">
-        <v>0.6261753800000001</v>
+        <v>0.6241735200000001</v>
       </c>
       <c r="P69">
-        <v>5.63557842</v>
+        <v>5.617561680000001</v>
       </c>
       <c r="Q69">
-        <v>6.17257842</v>
+        <v>6.15456168</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.391610740312822</v>
+        <v>0.4020350994460462</v>
       </c>
       <c r="T69">
-        <v>2.114935439599562</v>
+        <v>2.178689522384918</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.668608790839444</v>
+        <v>5.585246896856511</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6964,22 +6964,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1624948318227347</v>
+        <v>0.1624122193422383</v>
       </c>
       <c r="C70">
-        <v>13.32665542709799</v>
+        <v>12.99153543074714</v>
       </c>
       <c r="D70">
-        <v>37.94265542709799</v>
+        <v>37.96953543074714</v>
       </c>
       <c r="E70">
-        <v>24.616</v>
+        <v>24.97800000000001</v>
       </c>
       <c r="F70">
-        <v>24.616</v>
+        <v>24.97800000000001</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7000,28 +7000,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M70">
-        <v>1.3612648</v>
+        <v>1.3812834</v>
       </c>
       <c r="N70">
-        <v>6.241735200000001</v>
+        <v>6.221716600000001</v>
       </c>
       <c r="O70">
-        <v>0.6241735200000001</v>
+        <v>0.6221716600000001</v>
       </c>
       <c r="P70">
-        <v>5.617561680000001</v>
+        <v>5.59954494</v>
       </c>
       <c r="Q70">
-        <v>6.15456168</v>
+        <v>6.13654494</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4020350994460462</v>
+        <v>0.4131319978781879</v>
       </c>
       <c r="T70">
-        <v>2.178689522384918</v>
+        <v>2.246556771801588</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.585246896856511</v>
+        <v>5.504301289655692</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7046,22 +7046,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1624122193422383</v>
+        <v>0.1623296068617417</v>
       </c>
       <c r="C71">
-        <v>12.99153543074714</v>
+        <v>12.65645354700712</v>
       </c>
       <c r="D71">
-        <v>37.96953543074714</v>
+        <v>37.99645354700712</v>
       </c>
       <c r="E71">
-        <v>24.97800000000001</v>
+        <v>25.34</v>
       </c>
       <c r="F71">
-        <v>24.97800000000001</v>
+        <v>25.34</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7082,28 +7082,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M71">
-        <v>1.3812834</v>
+        <v>1.401302</v>
       </c>
       <c r="N71">
-        <v>6.221716600000001</v>
+        <v>6.201698</v>
       </c>
       <c r="O71">
-        <v>0.6221716600000001</v>
+        <v>0.6201698000000001</v>
       </c>
       <c r="P71">
-        <v>5.59954494</v>
+        <v>5.5815282</v>
       </c>
       <c r="Q71">
-        <v>6.13654494</v>
+        <v>6.1185282</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4131319978781879</v>
+        <v>0.4249686895391392</v>
       </c>
       <c r="T71">
-        <v>2.246556771801588</v>
+        <v>2.318948504512703</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.504301289655692</v>
+        <v>5.425668414089182</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7128,22 +7128,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1623296068617417</v>
+        <v>0.1622469943812453</v>
       </c>
       <c r="C72">
-        <v>12.65645354700712</v>
+        <v>12.32140985699406</v>
       </c>
       <c r="D72">
-        <v>37.99645354700712</v>
+        <v>38.02340985699406</v>
       </c>
       <c r="E72">
-        <v>25.34</v>
+        <v>25.70200000000001</v>
       </c>
       <c r="F72">
-        <v>25.34</v>
+        <v>25.70200000000001</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7164,28 +7164,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M72">
-        <v>1.401302</v>
+        <v>1.4213206</v>
       </c>
       <c r="N72">
-        <v>6.201698</v>
+        <v>6.1816794</v>
       </c>
       <c r="O72">
-        <v>0.6201698000000001</v>
+        <v>0.6181679400000001</v>
       </c>
       <c r="P72">
-        <v>5.5815282</v>
+        <v>5.56351146</v>
       </c>
       <c r="Q72">
-        <v>6.1185282</v>
+        <v>6.10051146</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4249686895391392</v>
+        <v>0.4376217047629148</v>
       </c>
       <c r="T72">
-        <v>2.318948504512703</v>
+        <v>2.396332770514239</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.425668414089182</v>
+        <v>5.349250549102011</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7210,22 +7210,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1622469943812453</v>
+        <v>0.1621643819007488</v>
       </c>
       <c r="C73">
-        <v>12.32140985699406</v>
+        <v>11.98640444205446</v>
       </c>
       <c r="D73">
-        <v>38.02340985699406</v>
+        <v>38.05040444205446</v>
       </c>
       <c r="E73">
-        <v>25.702</v>
+        <v>26.064</v>
       </c>
       <c r="F73">
-        <v>25.702</v>
+        <v>26.064</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7246,28 +7246,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M73">
-        <v>1.4213206</v>
+        <v>1.4413392</v>
       </c>
       <c r="N73">
-        <v>6.1816794</v>
+        <v>6.161660800000001</v>
       </c>
       <c r="O73">
-        <v>0.6181679400000001</v>
+        <v>0.6161660800000002</v>
       </c>
       <c r="P73">
-        <v>5.56351146</v>
+        <v>5.545494720000001</v>
       </c>
       <c r="Q73">
-        <v>6.10051146</v>
+        <v>6.082494720000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4376217047629147</v>
+        <v>0.4511785067883884</v>
       </c>
       <c r="T73">
-        <v>2.396332770514238</v>
+        <v>2.479244484087313</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.349250549102011</v>
+        <v>5.274955402586706</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7292,22 +7292,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1621643819007488</v>
+        <v>0.1620817694202523</v>
       </c>
       <c r="C74">
-        <v>11.98640444205446</v>
+        <v>11.65143738376601</v>
       </c>
       <c r="D74">
-        <v>38.05040444205446</v>
+        <v>38.07743738376601</v>
       </c>
       <c r="E74">
-        <v>26.064</v>
+        <v>26.426</v>
       </c>
       <c r="F74">
-        <v>26.064</v>
+        <v>26.426</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7328,28 +7328,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M74">
-        <v>1.4413392</v>
+        <v>1.4613578</v>
       </c>
       <c r="N74">
-        <v>6.161660800000001</v>
+        <v>6.141642200000001</v>
       </c>
       <c r="O74">
-        <v>0.6161660800000002</v>
+        <v>0.6141642200000001</v>
       </c>
       <c r="P74">
-        <v>5.545494720000001</v>
+        <v>5.52747798</v>
       </c>
       <c r="Q74">
-        <v>6.082494720000001</v>
+        <v>6.06447798</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4511785067883884</v>
+        <v>0.4657395163713046</v>
       </c>
       <c r="T74">
-        <v>2.479244484087313</v>
+        <v>2.568297806073208</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.274955402586706</v>
+        <v>5.202695739537572</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7374,22 +7374,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1620817694202523</v>
+        <v>0.1619991569397558</v>
       </c>
       <c r="C75">
-        <v>11.65143738376601</v>
+        <v>11.31650876393838</v>
       </c>
       <c r="D75">
-        <v>38.07743738376601</v>
+        <v>38.10450876393838</v>
       </c>
       <c r="E75">
-        <v>26.426</v>
+        <v>26.788</v>
       </c>
       <c r="F75">
-        <v>26.426</v>
+        <v>26.788</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7410,28 +7410,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M75">
-        <v>1.4613578</v>
+        <v>1.4813764</v>
       </c>
       <c r="N75">
-        <v>6.141642200000001</v>
+        <v>6.1216236</v>
       </c>
       <c r="O75">
-        <v>0.6141642200000001</v>
+        <v>0.6121623600000001</v>
       </c>
       <c r="P75">
-        <v>5.52747798</v>
+        <v>5.50946124</v>
       </c>
       <c r="Q75">
-        <v>6.06447798</v>
+        <v>6.04646124</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4657395163713046</v>
+        <v>0.4814206036144452</v>
       </c>
       <c r="T75">
-        <v>2.568297806073208</v>
+        <v>2.664201383596479</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.202695739537572</v>
+        <v>5.132389040354632</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7456,22 +7456,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1619991569397558</v>
+        <v>0.1619165444592593</v>
       </c>
       <c r="C76">
-        <v>11.31650876393838</v>
+        <v>10.98161866461401</v>
       </c>
       <c r="D76">
-        <v>38.10450876393838</v>
+        <v>38.13161866461402</v>
       </c>
       <c r="E76">
-        <v>26.788</v>
+        <v>27.15</v>
       </c>
       <c r="F76">
-        <v>26.788</v>
+        <v>27.15</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7492,28 +7492,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M76">
-        <v>1.4813764</v>
+        <v>1.501395</v>
       </c>
       <c r="N76">
-        <v>6.1216236</v>
+        <v>6.101605</v>
       </c>
       <c r="O76">
-        <v>0.6121623600000001</v>
+        <v>0.6101605000000001</v>
       </c>
       <c r="P76">
-        <v>5.50946124</v>
+        <v>5.4914445</v>
       </c>
       <c r="Q76">
-        <v>6.04646124</v>
+        <v>6.0284445</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4814206036144452</v>
+        <v>0.4983561778370371</v>
       </c>
       <c r="T76">
-        <v>2.664201383596479</v>
+        <v>2.767777247321612</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.132389040354632</v>
+        <v>5.063957186483236</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7538,22 +7538,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1619165444592593</v>
+        <v>0.1618339319787628</v>
       </c>
       <c r="C77">
-        <v>10.98161866461401</v>
+        <v>10.64676716806907</v>
       </c>
       <c r="D77">
-        <v>38.13161866461402</v>
+        <v>38.15876716806908</v>
       </c>
       <c r="E77">
-        <v>27.15</v>
+        <v>27.512</v>
       </c>
       <c r="F77">
-        <v>27.15</v>
+        <v>27.512</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7574,28 +7574,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M77">
-        <v>1.501395</v>
+        <v>1.5214136</v>
       </c>
       <c r="N77">
-        <v>6.101605</v>
+        <v>6.081586400000001</v>
       </c>
       <c r="O77">
-        <v>0.6101605000000001</v>
+        <v>0.6081586400000001</v>
       </c>
       <c r="P77">
-        <v>5.4914445</v>
+        <v>5.473427760000001</v>
       </c>
       <c r="Q77">
-        <v>6.0284445</v>
+        <v>6.010427760000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4983561778370371</v>
+        <v>0.5167030499115116</v>
       </c>
       <c r="T77">
-        <v>2.767777247321612</v>
+        <v>2.87998443302384</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.063957186483236</v>
+        <v>4.997326170871616</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7620,22 +7620,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1618339319787628</v>
+        <v>0.1617513194982663</v>
       </c>
       <c r="C78">
-        <v>10.64676716806907</v>
+        <v>10.31195435681418</v>
       </c>
       <c r="D78">
-        <v>38.15876716806908</v>
+        <v>38.18595435681418</v>
       </c>
       <c r="E78">
-        <v>27.512</v>
+        <v>27.874</v>
       </c>
       <c r="F78">
-        <v>27.512</v>
+        <v>27.874</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7656,28 +7656,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M78">
-        <v>1.5214136</v>
+        <v>1.5414322</v>
       </c>
       <c r="N78">
-        <v>6.081586400000001</v>
+        <v>6.061567800000001</v>
       </c>
       <c r="O78">
-        <v>0.6081586400000001</v>
+        <v>0.6061567800000001</v>
       </c>
       <c r="P78">
-        <v>5.473427760000001</v>
+        <v>5.455411020000001</v>
       </c>
       <c r="Q78">
-        <v>6.010427760000001</v>
+        <v>5.99241102</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5167030499115116</v>
+        <v>0.5366453021663751</v>
       </c>
       <c r="T78">
-        <v>2.87998443302384</v>
+        <v>3.00194876530887</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.997326170871616</v>
+        <v>4.932425830990166</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7702,22 +7702,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1617513194982663</v>
+        <v>0.1616687070177698</v>
       </c>
       <c r="C79">
-        <v>10.31195435681418</v>
+        <v>9.977180313595227</v>
       </c>
       <c r="D79">
-        <v>38.18595435681418</v>
+        <v>38.21318031359523</v>
       </c>
       <c r="E79">
-        <v>27.874</v>
+        <v>28.236</v>
       </c>
       <c r="F79">
-        <v>27.874</v>
+        <v>28.236</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7738,28 +7738,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M79">
-        <v>1.5414322</v>
+        <v>1.5614508</v>
       </c>
       <c r="N79">
-        <v>6.061567800000001</v>
+        <v>6.0415492</v>
       </c>
       <c r="O79">
-        <v>0.6061567800000001</v>
+        <v>0.60415492</v>
       </c>
       <c r="P79">
-        <v>5.455411020000001</v>
+        <v>5.43739428</v>
       </c>
       <c r="Q79">
-        <v>5.99241102</v>
+        <v>5.97439428</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5366453021663751</v>
+        <v>0.5584004864444081</v>
       </c>
       <c r="T79">
-        <v>3.00194876530887</v>
+        <v>3.135000764165266</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.932425830990166</v>
+        <v>4.869189602387728</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7784,22 +7784,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1616687070177698</v>
+        <v>0.1615860945372733</v>
       </c>
       <c r="C80">
-        <v>9.977180313595227</v>
+        <v>9.642445121394321</v>
       </c>
       <c r="D80">
-        <v>38.21318031359523</v>
+        <v>38.24044512139432</v>
       </c>
       <c r="E80">
-        <v>28.236</v>
+        <v>28.598</v>
       </c>
       <c r="F80">
-        <v>28.236</v>
+        <v>28.598</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7820,28 +7820,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M80">
-        <v>1.5614508</v>
+        <v>1.5814694</v>
       </c>
       <c r="N80">
-        <v>6.0415492</v>
+        <v>6.0215306</v>
       </c>
       <c r="O80">
-        <v>0.60415492</v>
+        <v>0.60215306</v>
       </c>
       <c r="P80">
-        <v>5.43739428</v>
+        <v>5.41937754</v>
       </c>
       <c r="Q80">
-        <v>5.97439428</v>
+        <v>5.95637754</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5584004864444081</v>
+        <v>0.5822275930346347</v>
       </c>
       <c r="T80">
-        <v>3.135000764165266</v>
+        <v>3.280724381960367</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.869189602387728</v>
+        <v>4.807554290965099</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7866,22 +7866,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1615860945372733</v>
+        <v>0.1615034820567768</v>
       </c>
       <c r="C81">
-        <v>9.642445121394321</v>
+        <v>9.307748863430522</v>
       </c>
       <c r="D81">
-        <v>38.24044512139432</v>
+        <v>38.26774886343053</v>
       </c>
       <c r="E81">
-        <v>28.598</v>
+        <v>28.96</v>
       </c>
       <c r="F81">
-        <v>28.598</v>
+        <v>28.96</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7902,28 +7902,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M81">
-        <v>1.5814694</v>
+        <v>1.601488</v>
       </c>
       <c r="N81">
-        <v>6.0215306</v>
+        <v>6.001512</v>
       </c>
       <c r="O81">
-        <v>0.60215306</v>
+        <v>0.6001512</v>
       </c>
       <c r="P81">
-        <v>5.41937754</v>
+        <v>5.4013608</v>
       </c>
       <c r="Q81">
-        <v>5.95637754</v>
+        <v>5.9383608</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5822275930346347</v>
+        <v>0.608437410283884</v>
       </c>
       <c r="T81">
-        <v>3.280724381960367</v>
+        <v>3.441020361534978</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.807554290965099</v>
+        <v>4.747459862328034</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7948,22 +7948,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1615034820567768</v>
+        <v>0.1614208695762803</v>
       </c>
       <c r="C82">
-        <v>9.307748863430522</v>
+        <v>8.973091623160762</v>
       </c>
       <c r="D82">
-        <v>38.26774886343053</v>
+        <v>38.29509162316076</v>
       </c>
       <c r="E82">
-        <v>28.96</v>
+        <v>29.322</v>
       </c>
       <c r="F82">
-        <v>28.96</v>
+        <v>29.322</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -7984,28 +7984,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M82">
-        <v>1.601488</v>
+        <v>1.6215066</v>
       </c>
       <c r="N82">
-        <v>6.001512</v>
+        <v>5.981493400000001</v>
       </c>
       <c r="O82">
-        <v>0.6001512</v>
+        <v>0.5981493400000001</v>
       </c>
       <c r="P82">
-        <v>5.4013608</v>
+        <v>5.383344060000001</v>
       </c>
       <c r="Q82">
-        <v>5.9383608</v>
+        <v>5.920344060000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.608437410283884</v>
+        <v>0.6374061556646332</v>
       </c>
       <c r="T82">
-        <v>3.441020361534978</v>
+        <v>3.618189602117443</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.747459862328034</v>
+        <v>4.688849246743738</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8030,22 +8030,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1614208695762803</v>
+        <v>0.1613382570957838</v>
       </c>
       <c r="C83">
-        <v>8.973091623160762</v>
+        <v>8.638473484280638</v>
       </c>
       <c r="D83">
-        <v>38.29509162316076</v>
+        <v>38.32247348428064</v>
       </c>
       <c r="E83">
-        <v>29.322</v>
+        <v>29.684</v>
       </c>
       <c r="F83">
-        <v>29.322</v>
+        <v>29.684</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8066,28 +8066,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M83">
-        <v>1.6215066</v>
+        <v>1.6415252</v>
       </c>
       <c r="N83">
-        <v>5.981493400000001</v>
+        <v>5.9614748</v>
       </c>
       <c r="O83">
-        <v>0.5981493400000001</v>
+        <v>0.5961474800000001</v>
       </c>
       <c r="P83">
-        <v>5.383344060000001</v>
+        <v>5.36532732</v>
       </c>
       <c r="Q83">
-        <v>5.920344060000001</v>
+        <v>5.90232732</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6374061556646332</v>
+        <v>0.6695936505321323</v>
       </c>
       <c r="T83">
-        <v>3.618189602117443</v>
+        <v>3.815044313875737</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.688849246743738</v>
+        <v>4.631668158368814</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8112,22 +8112,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1613382570957838</v>
+        <v>0.1612556446152873</v>
       </c>
       <c r="C84">
-        <v>8.638473484280638</v>
+        <v>8.30389453072533</v>
       </c>
       <c r="D84">
-        <v>38.32247348428064</v>
+        <v>38.34989453072534</v>
       </c>
       <c r="E84">
-        <v>29.684</v>
+        <v>30.04600000000001</v>
       </c>
       <c r="F84">
-        <v>29.684</v>
+        <v>30.04600000000001</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8148,28 +8148,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M84">
-        <v>1.6415252</v>
+        <v>1.6615438</v>
       </c>
       <c r="N84">
-        <v>5.9614748</v>
+        <v>5.9414562</v>
       </c>
       <c r="O84">
-        <v>0.5961474800000001</v>
+        <v>0.59414562</v>
       </c>
       <c r="P84">
-        <v>5.36532732</v>
+        <v>5.34731058</v>
       </c>
       <c r="Q84">
-        <v>5.90232732</v>
+        <v>5.88431058</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6695936505321323</v>
+        <v>0.7055679095016901</v>
       </c>
       <c r="T84">
-        <v>3.815044313875737</v>
+        <v>4.035058403487948</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.631668158368814</v>
+        <v>4.575864927545092</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8194,22 +8194,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1612556446152873</v>
+        <v>0.1611730321347908</v>
       </c>
       <c r="C85">
-        <v>8.30389453072533</v>
+        <v>7.969354846670402</v>
       </c>
       <c r="D85">
-        <v>38.34989453072534</v>
+        <v>38.37735484667041</v>
       </c>
       <c r="E85">
-        <v>30.04600000000001</v>
+        <v>30.408</v>
       </c>
       <c r="F85">
-        <v>30.04600000000001</v>
+        <v>30.408</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8230,28 +8230,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M85">
-        <v>1.6615438</v>
+        <v>1.6815624</v>
       </c>
       <c r="N85">
-        <v>5.9414562</v>
+        <v>5.921437600000001</v>
       </c>
       <c r="O85">
-        <v>0.59414562</v>
+        <v>0.5921437600000001</v>
       </c>
       <c r="P85">
-        <v>5.34731058</v>
+        <v>5.329293840000001</v>
       </c>
       <c r="Q85">
-        <v>5.88431058</v>
+        <v>5.866293840000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7055679095016901</v>
+        <v>0.7460389508424428</v>
       </c>
       <c r="T85">
-        <v>4.035058403487948</v>
+        <v>4.282574254301686</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.575864927545092</v>
+        <v>4.52139034507432</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8276,22 +8276,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1611730321347908</v>
+        <v>0.1630029196542943</v>
       </c>
       <c r="C86">
-        <v>7.969354846670406</v>
+        <v>7.008169750662368</v>
       </c>
       <c r="D86">
-        <v>38.37735484667041</v>
+        <v>37.77816975066237</v>
       </c>
       <c r="E86">
-        <v>30.408</v>
+        <v>30.77</v>
       </c>
       <c r="F86">
-        <v>30.408</v>
+        <v>30.77</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8312,45 +8312,45 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M86">
-        <v>1.6815624</v>
+        <v>1.778506</v>
       </c>
       <c r="N86">
-        <v>5.921437600000001</v>
+        <v>5.824494000000001</v>
       </c>
       <c r="O86">
-        <v>0.5921437600000001</v>
+        <v>0.5824494000000001</v>
       </c>
       <c r="P86">
-        <v>5.329293840000001</v>
+        <v>5.242044600000001</v>
       </c>
       <c r="Q86">
-        <v>5.866293840000001</v>
+        <v>5.779044600000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7460389508424423</v>
+        <v>0.7919061310286286</v>
       </c>
       <c r="T86">
-        <v>4.282574254301683</v>
+        <v>4.563092218557252</v>
       </c>
       <c r="U86">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V86">
         <v>0.1</v>
       </c>
       <c r="W86">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y86">
-        <v>4.52139034507432</v>
+        <v>4.274936379185675</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8358,22 +8358,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1630029196542943</v>
+        <v>0.1629428071737978</v>
       </c>
       <c r="C87">
-        <v>7.008169750662368</v>
+        <v>6.665555827768753</v>
       </c>
       <c r="D87">
-        <v>37.77816975066237</v>
+        <v>37.79755582776875</v>
       </c>
       <c r="E87">
-        <v>30.77</v>
+        <v>31.132</v>
       </c>
       <c r="F87">
-        <v>30.77</v>
+        <v>31.132</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8394,28 +8394,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M87">
-        <v>1.778506</v>
+        <v>1.7994296</v>
       </c>
       <c r="N87">
-        <v>5.824494000000001</v>
+        <v>5.8035704</v>
       </c>
       <c r="O87">
-        <v>0.5824494000000001</v>
+        <v>0.58035704</v>
       </c>
       <c r="P87">
-        <v>5.242044600000001</v>
+        <v>5.22321336</v>
       </c>
       <c r="Q87">
-        <v>5.779044600000001</v>
+        <v>5.76021336</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7919061310286286</v>
+        <v>0.8443257655271271</v>
       </c>
       <c r="T87">
-        <v>4.563092218557252</v>
+        <v>4.883684177706474</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.274936379185675</v>
+        <v>4.225227816637005</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8440,22 +8440,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1629428071737978</v>
+        <v>0.1628826946933013</v>
       </c>
       <c r="C88">
-        <v>6.665555827768753</v>
+        <v>6.322961811235952</v>
       </c>
       <c r="D88">
-        <v>37.79755582776875</v>
+        <v>37.81696181123596</v>
       </c>
       <c r="E88">
-        <v>31.132</v>
+        <v>31.494</v>
       </c>
       <c r="F88">
-        <v>31.132</v>
+        <v>31.494</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8476,28 +8476,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M88">
-        <v>1.7994296</v>
+        <v>1.8203532</v>
       </c>
       <c r="N88">
-        <v>5.8035704</v>
+        <v>5.7826468</v>
       </c>
       <c r="O88">
-        <v>0.58035704</v>
+        <v>0.5782646800000001</v>
       </c>
       <c r="P88">
-        <v>5.22321336</v>
+        <v>5.20438212</v>
       </c>
       <c r="Q88">
-        <v>5.76021336</v>
+        <v>5.74138212</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8443257655271271</v>
+        <v>0.9048099591792408</v>
       </c>
       <c r="T88">
-        <v>4.883684177706474</v>
+        <v>5.253597976724807</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.225227816637005</v>
+        <v>4.176661979664166</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8522,22 +8522,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1628826946933013</v>
+        <v>0.1628225822128048</v>
       </c>
       <c r="C89">
-        <v>6.322961811235952</v>
+        <v>5.980387731740599</v>
       </c>
       <c r="D89">
-        <v>37.81696181123596</v>
+        <v>37.8363877317406</v>
       </c>
       <c r="E89">
-        <v>31.494</v>
+        <v>31.856</v>
       </c>
       <c r="F89">
-        <v>31.494</v>
+        <v>31.856</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8558,28 +8558,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M89">
-        <v>1.8203532</v>
+        <v>1.8412768</v>
       </c>
       <c r="N89">
-        <v>5.7826468</v>
+        <v>5.7617232</v>
       </c>
       <c r="O89">
-        <v>0.5782646800000001</v>
+        <v>0.5761723200000001</v>
       </c>
       <c r="P89">
-        <v>5.20438212</v>
+        <v>5.18555088</v>
       </c>
       <c r="Q89">
-        <v>5.74138212</v>
+        <v>5.72255088</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9048099591792408</v>
+        <v>0.9753748517733734</v>
       </c>
       <c r="T89">
-        <v>5.253597976724807</v>
+        <v>5.685164075579528</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.176661979664166</v>
+        <v>4.129199911713437</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8604,22 +8604,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1628225822128048</v>
+        <v>0.1627624697323083</v>
       </c>
       <c r="C90">
-        <v>5.980387731740599</v>
+        <v>5.63783362002242</v>
       </c>
       <c r="D90">
-        <v>37.8363877317406</v>
+        <v>37.85583362002242</v>
       </c>
       <c r="E90">
-        <v>31.856</v>
+        <v>32.218</v>
       </c>
       <c r="F90">
-        <v>31.856</v>
+        <v>32.218</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8640,28 +8640,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M90">
-        <v>1.8412768</v>
+        <v>1.8622004</v>
       </c>
       <c r="N90">
-        <v>5.7617232</v>
+        <v>5.740799600000001</v>
       </c>
       <c r="O90">
-        <v>0.5761723200000001</v>
+        <v>0.5740799600000001</v>
       </c>
       <c r="P90">
-        <v>5.18555088</v>
+        <v>5.166719640000001</v>
       </c>
       <c r="Q90">
-        <v>5.72255088</v>
+        <v>5.703719640000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9753748517733734</v>
+        <v>1.058769724839167</v>
       </c>
       <c r="T90">
-        <v>5.685164075579528</v>
+        <v>6.195196737862381</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.129199911713437</v>
+        <v>4.082804407087443</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8686,22 +8686,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1627624697323083</v>
+        <v>0.1627023572518118</v>
       </c>
       <c r="C91">
-        <v>5.63783362002242</v>
+        <v>5.295299506884412</v>
       </c>
       <c r="D91">
-        <v>37.85583362002242</v>
+        <v>37.87529950688442</v>
       </c>
       <c r="E91">
-        <v>32.218</v>
+        <v>32.58000000000001</v>
       </c>
       <c r="F91">
-        <v>32.218</v>
+        <v>32.58000000000001</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8722,28 +8722,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M91">
-        <v>1.8622004</v>
+        <v>1.883124</v>
       </c>
       <c r="N91">
-        <v>5.740799600000001</v>
+        <v>5.719876</v>
       </c>
       <c r="O91">
-        <v>0.5740799600000001</v>
+        <v>0.5719876</v>
       </c>
       <c r="P91">
-        <v>5.166719640000001</v>
+        <v>5.1478884</v>
       </c>
       <c r="Q91">
-        <v>5.703719640000001</v>
+        <v>5.6848884</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.058769724839167</v>
+        <v>1.158843572518118</v>
       </c>
       <c r="T91">
-        <v>6.195196737862381</v>
+        <v>6.807235932601804</v>
       </c>
       <c r="U91">
         <v>0.0578</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.082804407087443</v>
+        <v>4.03743991367536</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8768,22 +8768,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1627023572518118</v>
+        <v>0.1655087447713153</v>
       </c>
       <c r="C92">
-        <v>5.295299506884412</v>
+        <v>4.045371327229418</v>
       </c>
       <c r="D92">
-        <v>37.87529950688442</v>
+        <v>36.98737132722942</v>
       </c>
       <c r="E92">
-        <v>32.58000000000001</v>
+        <v>32.942</v>
       </c>
       <c r="F92">
-        <v>32.58000000000001</v>
+        <v>32.942</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8804,45 +8804,45 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M92">
-        <v>1.883124</v>
+        <v>2.0193446</v>
       </c>
       <c r="N92">
-        <v>5.719876</v>
+        <v>5.5836554</v>
       </c>
       <c r="O92">
-        <v>0.5719876</v>
+        <v>0.55836554</v>
       </c>
       <c r="P92">
-        <v>5.1478884</v>
+        <v>5.025289860000001</v>
       </c>
       <c r="Q92">
-        <v>5.6848884</v>
+        <v>5.562289860000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.158843572518118</v>
+        <v>1.281156053014615</v>
       </c>
       <c r="T92">
-        <v>6.807235932601804</v>
+        <v>7.555283837283322</v>
       </c>
       <c r="U92">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V92">
         <v>0.1</v>
       </c>
       <c r="W92">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y92">
-        <v>4.03743991367536</v>
+        <v>3.765082987816938</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8850,22 +8850,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1655087447713153</v>
+        <v>0.1654801322908189</v>
       </c>
       <c r="C93">
-        <v>4.045371327229418</v>
+        <v>3.692214068463564</v>
       </c>
       <c r="D93">
-        <v>36.98737132722942</v>
+        <v>36.99621406846357</v>
       </c>
       <c r="E93">
-        <v>32.942</v>
+        <v>33.304</v>
       </c>
       <c r="F93">
-        <v>32.942</v>
+        <v>33.304</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8886,28 +8886,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M93">
-        <v>2.0193446</v>
+        <v>2.0415352</v>
       </c>
       <c r="N93">
-        <v>5.5836554</v>
+        <v>5.5614648</v>
       </c>
       <c r="O93">
-        <v>0.55836554</v>
+        <v>0.5561464800000001</v>
       </c>
       <c r="P93">
-        <v>5.025289860000001</v>
+        <v>5.005318320000001</v>
       </c>
       <c r="Q93">
-        <v>5.562289860000001</v>
+        <v>5.542318320000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.281156053014615</v>
+        <v>1.434046653635236</v>
       </c>
       <c r="T93">
-        <v>7.555283837283322</v>
+        <v>8.490343718135222</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.765082987816938</v>
+        <v>3.724158172731971</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8932,22 +8932,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1654801322908189</v>
+        <v>0.1654515198103224</v>
       </c>
       <c r="C94">
-        <v>3.692214068463564</v>
+        <v>3.33906103885856</v>
       </c>
       <c r="D94">
-        <v>36.99621406846357</v>
+        <v>37.00506103885856</v>
       </c>
       <c r="E94">
-        <v>33.304</v>
+        <v>33.666</v>
       </c>
       <c r="F94">
-        <v>33.304</v>
+        <v>33.666</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8968,28 +8968,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M94">
-        <v>2.0415352</v>
+        <v>2.0637258</v>
       </c>
       <c r="N94">
-        <v>5.5614648</v>
+        <v>5.5392742</v>
       </c>
       <c r="O94">
-        <v>0.5561464800000001</v>
+        <v>0.5539274200000001</v>
       </c>
       <c r="P94">
-        <v>5.005318320000001</v>
+        <v>4.98534678</v>
       </c>
       <c r="Q94">
-        <v>5.542318320000001</v>
+        <v>5.52234678</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.434046653635236</v>
+        <v>1.630620283004606</v>
       </c>
       <c r="T94">
-        <v>8.490343718135222</v>
+        <v>9.692563564944804</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.724158172731971</v>
+        <v>3.684113461197219</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9014,22 +9014,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1654515198103224</v>
+        <v>0.1654229073298258</v>
       </c>
       <c r="C95">
-        <v>3.33906103885856</v>
+        <v>2.985912241449107</v>
       </c>
       <c r="D95">
-        <v>37.00506103885856</v>
+        <v>37.01391224144911</v>
       </c>
       <c r="E95">
-        <v>33.666</v>
+        <v>34.02800000000001</v>
       </c>
       <c r="F95">
-        <v>33.666</v>
+        <v>34.02800000000001</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9050,28 +9050,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M95">
-        <v>2.0637258</v>
+        <v>2.0859164</v>
       </c>
       <c r="N95">
-        <v>5.5392742</v>
+        <v>5.5170836</v>
       </c>
       <c r="O95">
-        <v>0.5539274200000001</v>
+        <v>0.55170836</v>
       </c>
       <c r="P95">
-        <v>4.98534678</v>
+        <v>4.96537524</v>
       </c>
       <c r="Q95">
-        <v>5.52234678</v>
+        <v>5.50237524</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.630620283004606</v>
+        <v>1.892718455497099</v>
       </c>
       <c r="T95">
-        <v>9.692563564944804</v>
+        <v>11.29552336069091</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.684113461197219</v>
+        <v>3.644920764801504</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9096,22 +9096,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1654229073298258</v>
+        <v>0.1653942948493294</v>
       </c>
       <c r="C96">
-        <v>2.985912241449107</v>
+        <v>2.632767679272796</v>
       </c>
       <c r="D96">
-        <v>37.01391224144911</v>
+        <v>37.0227676792728</v>
       </c>
       <c r="E96">
-        <v>34.02800000000001</v>
+        <v>34.39000000000001</v>
       </c>
       <c r="F96">
-        <v>34.02800000000001</v>
+        <v>34.39000000000001</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9132,28 +9132,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M96">
-        <v>2.0859164</v>
+        <v>2.108107</v>
       </c>
       <c r="N96">
-        <v>5.5170836</v>
+        <v>5.494893</v>
       </c>
       <c r="O96">
-        <v>0.55170836</v>
+        <v>0.5494893000000001</v>
       </c>
       <c r="P96">
-        <v>4.96537524</v>
+        <v>4.9454037</v>
       </c>
       <c r="Q96">
-        <v>5.50237524</v>
+        <v>5.4824037</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.892718455497099</v>
+        <v>2.25965589698659</v>
       </c>
       <c r="T96">
-        <v>11.29552336069091</v>
+        <v>13.53966707473547</v>
       </c>
       <c r="U96">
         <v>0.0613</v>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.644920764801504</v>
+        <v>3.606553177803593</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9178,22 +9178,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1653942948493294</v>
+        <v>0.1653656823688328</v>
       </c>
       <c r="C97">
-        <v>2.632767679272796</v>
+        <v>2.279627355370188</v>
       </c>
       <c r="D97">
-        <v>37.0227676792728</v>
+        <v>37.03162735537019</v>
       </c>
       <c r="E97">
-        <v>34.39000000000001</v>
+        <v>34.752</v>
       </c>
       <c r="F97">
-        <v>34.39000000000001</v>
+        <v>34.752</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9214,28 +9214,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M97">
-        <v>2.108107</v>
+        <v>2.1302976</v>
       </c>
       <c r="N97">
-        <v>5.494893</v>
+        <v>5.472702400000001</v>
       </c>
       <c r="O97">
-        <v>0.5494893000000001</v>
+        <v>0.5472702400000001</v>
       </c>
       <c r="P97">
-        <v>4.9454037</v>
+        <v>4.925432160000001</v>
       </c>
       <c r="Q97">
-        <v>5.4824037</v>
+        <v>5.462432160000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.25965589698659</v>
+        <v>2.810062059220826</v>
       </c>
       <c r="T97">
-        <v>13.53966707473547</v>
+        <v>16.90588264580231</v>
       </c>
       <c r="U97">
         <v>0.0613</v>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.606553177803593</v>
+        <v>3.568984915534807</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9260,22 +9260,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1653656823688328</v>
+        <v>0.1653370698883364</v>
       </c>
       <c r="C98">
-        <v>2.279627355370188</v>
+        <v>1.926491272784659</v>
       </c>
       <c r="D98">
-        <v>37.03162735537019</v>
+        <v>37.04049127278466</v>
       </c>
       <c r="E98">
-        <v>34.752</v>
+        <v>35.114</v>
       </c>
       <c r="F98">
-        <v>34.752</v>
+        <v>35.114</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9296,28 +9296,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M98">
-        <v>2.1302976</v>
+        <v>2.1524882</v>
       </c>
       <c r="N98">
-        <v>5.472702400000001</v>
+        <v>5.450511800000001</v>
       </c>
       <c r="O98">
-        <v>0.5472702400000001</v>
+        <v>0.5450511800000001</v>
       </c>
       <c r="P98">
-        <v>4.925432160000001</v>
+        <v>4.905460620000001</v>
       </c>
       <c r="Q98">
-        <v>5.462432160000001</v>
+        <v>5.442460620000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.810062059220818</v>
+        <v>3.727405662944542</v>
       </c>
       <c r="T98">
-        <v>16.90588264580227</v>
+        <v>22.51624193091364</v>
       </c>
       <c r="U98">
         <v>0.0613</v>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.568984915534807</v>
+        <v>3.532191256611767</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9342,22 +9342,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1653370698883364</v>
+        <v>0.1677780574078399</v>
       </c>
       <c r="C99">
-        <v>1.926491272784659</v>
+        <v>0.8232483079878392</v>
       </c>
       <c r="D99">
-        <v>37.04049127278466</v>
+        <v>36.29924830798784</v>
       </c>
       <c r="E99">
-        <v>35.114</v>
+        <v>35.476</v>
       </c>
       <c r="F99">
-        <v>35.114</v>
+        <v>35.476</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9378,45 +9378,45 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M99">
-        <v>2.1524882</v>
+        <v>2.2740116</v>
       </c>
       <c r="N99">
-        <v>5.450511800000001</v>
+        <v>5.3289884</v>
       </c>
       <c r="O99">
-        <v>0.5450511800000001</v>
+        <v>0.53289884</v>
       </c>
       <c r="P99">
-        <v>4.905460620000001</v>
+        <v>4.79608956</v>
       </c>
       <c r="Q99">
-        <v>5.442460620000001</v>
+        <v>5.33308956</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.727405662944542</v>
+        <v>5.562092870391988</v>
       </c>
       <c r="T99">
-        <v>22.51624193091364</v>
+        <v>33.73696050113638</v>
       </c>
       <c r="U99">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V99">
         <v>0.1</v>
       </c>
       <c r="W99">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y99">
-        <v>3.532191256611767</v>
+        <v>3.343430613986314</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9424,22 +9424,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1677780574078399</v>
+        <v>0.1677746449273434</v>
       </c>
       <c r="C100">
-        <v>0.8232483079878392</v>
+        <v>0.4622638508243071</v>
       </c>
       <c r="D100">
-        <v>36.29924830798784</v>
+        <v>36.30026385082431</v>
       </c>
       <c r="E100">
-        <v>35.476</v>
+        <v>35.838</v>
       </c>
       <c r="F100">
-        <v>35.476</v>
+        <v>35.838</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9460,28 +9460,28 @@
         <v>7.603000000000001</v>
       </c>
       <c r="M100">
-        <v>2.2740116</v>
+        <v>2.2972158</v>
       </c>
       <c r="N100">
-        <v>5.3289884</v>
+        <v>5.305784200000001</v>
       </c>
       <c r="O100">
-        <v>0.53289884</v>
+        <v>0.5305784200000001</v>
       </c>
       <c r="P100">
-        <v>4.79608956</v>
+        <v>4.77520578</v>
       </c>
       <c r="Q100">
-        <v>5.33308956</v>
+        <v>5.31220578</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.562092870391988</v>
+        <v>11.06615449273433</v>
       </c>
       <c r="T100">
-        <v>33.73696050113638</v>
+        <v>67.39911621180461</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9498,91 +9498,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.343430613986314</v>
+        <v>3.309658587582412</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1677746449273434</v>
-      </c>
-      <c r="C101">
-        <v>0.4622638508243071</v>
-      </c>
-      <c r="D101">
-        <v>36.30026385082431</v>
-      </c>
-      <c r="E101">
-        <v>35.838</v>
-      </c>
-      <c r="F101">
-        <v>35.838</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>36.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="K101">
-        <v>0.537</v>
-      </c>
-      <c r="L101">
-        <v>7.603000000000001</v>
-      </c>
-      <c r="M101">
-        <v>2.2972158</v>
-      </c>
-      <c r="N101">
-        <v>5.305784200000001</v>
-      </c>
-      <c r="O101">
-        <v>0.5305784200000001</v>
-      </c>
-      <c r="P101">
-        <v>4.77520578</v>
-      </c>
-      <c r="Q101">
-        <v>5.31220578</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.06615449273433</v>
-      </c>
-      <c r="T101">
-        <v>67.39911621180461</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.1</v>
-      </c>
-      <c r="W101">
-        <v>0.05769000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.309658587582412</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
